--- a/report/templates/ВОР_с_расценками.xlsx
+++ b/report/templates/ВОР_с_расценками.xlsx
@@ -1128,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:HL853"/>
+  <dimension ref="A1:HL858"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="9.109375" customWidth="1" style="136" min="1" max="1"/>
@@ -62618,6 +62618,186 @@
       <c r="HK853" s="16" t="n"/>
       <c r="HL853" s="16" t="n"/>
     </row>
+    <row r="854">
+      <c r="A854" s="33" t="inlineStr">
+        <is>
+          <t>3 этап</t>
+        </is>
+      </c>
+      <c r="B854" s="34" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="C854" s="35" t="inlineStr">
+        <is>
+          <t>Устройство монолитного железобетонного перекрытия здания Общежития</t>
+        </is>
+      </c>
+      <c r="D854" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E854" s="144" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="F854" s="145" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G854" s="145" t="n">
+        <v>16688000</v>
+      </c>
+      <c r="H854" s="10" t="inlineStr">
+        <is>
+          <t>По аналогу 3.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="33" t="inlineStr">
+        <is>
+          <t>3 этап</t>
+        </is>
+      </c>
+      <c r="B855" s="34" t="inlineStr">
+        <is>
+          <t>3.3.2.1</t>
+        </is>
+      </c>
+      <c r="C855" s="35" t="inlineStr">
+        <is>
+          <t>Армирование плиты перекрытия арматурой ø8А500С, отм. +6,590</t>
+        </is>
+      </c>
+      <c r="D855" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E855" s="144" t="n">
+        <v>7981.29</v>
+      </c>
+      <c r="F855" s="145" t="n">
+        <v>100</v>
+      </c>
+      <c r="G855" s="145" t="n">
+        <v>798129</v>
+      </c>
+      <c r="H855" s="10" t="inlineStr">
+        <is>
+          <t>Экспертная оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="33" t="inlineStr">
+        <is>
+          <t>3 этап</t>
+        </is>
+      </c>
+      <c r="B856" s="34" t="inlineStr">
+        <is>
+          <t>3.3.2.2</t>
+        </is>
+      </c>
+      <c r="C856" s="35" t="inlineStr">
+        <is>
+          <t>Армирование плиты перекрытия арматурой ø8А500С, отм. +9,930</t>
+        </is>
+      </c>
+      <c r="D856" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E856" s="144" t="n">
+        <v>7982.29</v>
+      </c>
+      <c r="F856" s="145" t="n">
+        <v>100</v>
+      </c>
+      <c r="G856" s="145" t="n">
+        <v>798229</v>
+      </c>
+      <c r="H856" s="10" t="inlineStr">
+        <is>
+          <t>Экспертная оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="33" t="inlineStr">
+        <is>
+          <t>3 этап</t>
+        </is>
+      </c>
+      <c r="B857" s="34" t="inlineStr">
+        <is>
+          <t>3.3.6</t>
+        </is>
+      </c>
+      <c r="C857" s="35" t="inlineStr">
+        <is>
+          <t>Устройство монолитного железобетонного перекрытия переходной Галереи</t>
+        </is>
+      </c>
+      <c r="D857" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E857" s="144" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F857" s="145" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G857" s="145" t="n">
+        <v>224000</v>
+      </c>
+      <c r="H857" s="10" t="inlineStr">
+        <is>
+          <t>По аналогу 3.2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="33" t="inlineStr">
+        <is>
+          <t>7 этап</t>
+        </is>
+      </c>
+      <c r="B858" s="34" t="inlineStr">
+        <is>
+          <t>7.2.1.1</t>
+        </is>
+      </c>
+      <c r="C858" s="35" t="inlineStr">
+        <is>
+          <t>Разработка грунта</t>
+        </is>
+      </c>
+      <c r="D858" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E858" s="144" t="n">
+        <v>887.7</v>
+      </c>
+      <c r="F858" s="145" t="n">
+        <v>11800</v>
+      </c>
+      <c r="G858" s="145" t="n">
+        <v>10474860</v>
+      </c>
+      <c r="H858" s="10" t="inlineStr">
+        <is>
+          <t>По аналогичным земляным работам</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0"/>

--- a/report/templates/ВОР_с_расценками.xlsx
+++ b/report/templates/ВОР_с_расценками.xlsx
@@ -1128,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:HL858"/>
+  <dimension ref="A1:HL1117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="9.109375" customWidth="1" style="136" min="1" max="1"/>
@@ -62798,6 +62798,6716 @@
         </is>
       </c>
     </row>
+    <row r="859">
+      <c r="A859" s="33" t="n">
+        <v>686</v>
+      </c>
+      <c r="B859" s="34" t="inlineStr">
+        <is>
+          <t>2.1.9.1</t>
+        </is>
+      </c>
+      <c r="C859" s="35" t="inlineStr">
+        <is>
+          <t>Перевозка и складирование грунта на обратную засыпку внутри ленточного фундамента и пазух котлована</t>
+        </is>
+      </c>
+      <c r="D859" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E859" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F859" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="33" t="n">
+        <v>687</v>
+      </c>
+      <c r="B860" s="34" t="inlineStr">
+        <is>
+          <t>2.2.3.1</t>
+        </is>
+      </c>
+      <c r="C860" s="35" t="inlineStr">
+        <is>
+          <t>Устройство армокаркаса в осях А-Г/1-10 на отм. -1,700/0,000</t>
+        </is>
+      </c>
+      <c r="D860" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E860" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F860" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="33" t="n">
+        <v>688</v>
+      </c>
+      <c r="B861" s="34" t="inlineStr">
+        <is>
+          <t>2.2.3.2</t>
+        </is>
+      </c>
+      <c r="C861" s="35" t="inlineStr">
+        <is>
+          <t>Устройство опалубки в осях А-Г/1-10 на отм. -1,700/0,000</t>
+        </is>
+      </c>
+      <c r="D861" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E861" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F861" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="33" t="n">
+        <v>689</v>
+      </c>
+      <c r="B862" s="34" t="inlineStr">
+        <is>
+          <t>2.2.3.3</t>
+        </is>
+      </c>
+      <c r="C862" s="35" t="inlineStr">
+        <is>
+          <t>Гидроизоляция битумной мастикой в 2 слоя подпорной стены и подколонников фундамента с внутренней стороны в осях  А-Г/1-10</t>
+        </is>
+      </c>
+      <c r="D862" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E862" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F862" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="33" t="n">
+        <v>690</v>
+      </c>
+      <c r="B863" s="34" t="inlineStr">
+        <is>
+          <t>2.2.7.3</t>
+        </is>
+      </c>
+      <c r="C863" s="35" t="inlineStr">
+        <is>
+          <t>Гидроизоляция битумной мастикой в 2 слоя подпорной стены и подколонников фундамента с внутренней стороны в осях  А-Г/1-10</t>
+        </is>
+      </c>
+      <c r="D863" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E863" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F863" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="33" t="n">
+        <v>691</v>
+      </c>
+      <c r="B864" s="34" t="inlineStr">
+        <is>
+          <t>2.4.2.1</t>
+        </is>
+      </c>
+      <c r="C864" s="35" t="inlineStr">
+        <is>
+          <t>Армирование  арматурой  ø8А500С с шагом 200 мм плиты перекрытия в осях А-Г/1-10 на отм. +3,100/+3,230</t>
+        </is>
+      </c>
+      <c r="D864" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E864" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F864" s="145" t="n">
+        <v>74543.75</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="33" t="n">
+        <v>692</v>
+      </c>
+      <c r="B865" s="34" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="C865" s="35" t="inlineStr">
+        <is>
+          <t>Устройство несъемной опалубки из профлиста Н-60-845 (ОЦ-01-БЦ) 0,8мм</t>
+        </is>
+      </c>
+      <c r="D865" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E865" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F865" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="33" t="n">
+        <v>693</v>
+      </c>
+      <c r="B866" s="34" t="inlineStr">
+        <is>
+          <t>3.3.3</t>
+        </is>
+      </c>
+      <c r="C866" s="35" t="inlineStr">
+        <is>
+          <t>Устройство несъемной опалубки из профлиста Н-60-845 (ОЦ-01-БЦ) 0,8мм</t>
+        </is>
+      </c>
+      <c r="D866" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E866" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F866" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="33" t="n">
+        <v>694</v>
+      </c>
+      <c r="B867" s="34" t="inlineStr">
+        <is>
+          <t>3.3.4</t>
+        </is>
+      </c>
+      <c r="C867" s="35" t="inlineStr">
+        <is>
+          <t>Устройство монолитного железобетонного перекрытия  здания АБК: торцевая опалубка, армирование, бетонирование,</t>
+        </is>
+      </c>
+      <c r="D867" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E867" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F867" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="33" t="n">
+        <v>695</v>
+      </c>
+      <c r="B868" s="34" t="inlineStr">
+        <is>
+          <t>3.3.4.1</t>
+        </is>
+      </c>
+      <c r="C868" s="35" t="inlineStr">
+        <is>
+          <t>Распалубка опалубки плиты покрытия в осях А-Г/1-10 на отм. +7,650 по периметрут здания</t>
+        </is>
+      </c>
+      <c r="D868" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E868" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F868" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="33" t="n">
+        <v>696</v>
+      </c>
+      <c r="B869" s="34" t="inlineStr">
+        <is>
+          <t>3.3.5</t>
+        </is>
+      </c>
+      <c r="C869" s="35" t="inlineStr">
+        <is>
+          <t>Устройство несъемной опалубки из профлиста Н-60-845 (ОЦ-01-БЦ) 0,8мм</t>
+        </is>
+      </c>
+      <c r="D869" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E869" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F869" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="33" t="n">
+        <v>697</v>
+      </c>
+      <c r="B870" s="34" t="inlineStr">
+        <is>
+          <t>3.3.6.1</t>
+        </is>
+      </c>
+      <c r="C870" s="35" t="inlineStr">
+        <is>
+          <t>Армирование  арматурой  ø8А500С с шагом 200 мм плиты перекрытия галереи на отм +3,260</t>
+        </is>
+      </c>
+      <c r="D870" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E870" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F870" s="145" t="n">
+        <v>35806.25</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="33" t="n">
+        <v>698</v>
+      </c>
+      <c r="B871" s="34" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="C871" s="35" t="inlineStr">
+        <is>
+          <t>Изготовление, поставка и монтаж наружных дверей 2300-1450 (Металлическая)</t>
+        </is>
+      </c>
+      <c r="D871" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E871" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F871" s="145" t="n">
+        <v>4106.67</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="33" t="n">
+        <v>699</v>
+      </c>
+      <c r="B872" s="34" t="inlineStr">
+        <is>
+          <t>4.4.2</t>
+        </is>
+      </c>
+      <c r="C872" s="35" t="inlineStr">
+        <is>
+          <t>Изготовление, поставка и монтаж наружных дверей 2300-1000 (металлическая противопожарная EI-30)</t>
+        </is>
+      </c>
+      <c r="D872" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E872" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F872" s="145" t="n">
+        <v>4106.67</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="33" t="n">
+        <v>700</v>
+      </c>
+      <c r="B873" s="34" t="inlineStr">
+        <is>
+          <t>4.4.3</t>
+        </is>
+      </c>
+      <c r="C873" s="35" t="inlineStr">
+        <is>
+          <t>Изготовление, поставка и монтаж наружных дверей 2100-1000 (Металлическая)</t>
+        </is>
+      </c>
+      <c r="D873" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E873" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F873" s="145" t="n">
+        <v>4106.67</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="33" t="n">
+        <v>701</v>
+      </c>
+      <c r="B874" s="34" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="C874" s="35" t="inlineStr">
+        <is>
+          <t>Изготовление, поставка и монтаж наружных дверей 2300-1450 (металлическая противопожарная EI-45)</t>
+        </is>
+      </c>
+      <c r="D874" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E874" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F874" s="145" t="n">
+        <v>4106.67</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="33" t="n">
+        <v>702</v>
+      </c>
+      <c r="B875" s="34" t="inlineStr">
+        <is>
+          <t>4.4.5</t>
+        </is>
+      </c>
+      <c r="C875" s="35" t="inlineStr">
+        <is>
+          <t>Изготовление, поставка и монтаж наружных дверей 2300-1000 (металлическая противопожарная EI-30)</t>
+        </is>
+      </c>
+      <c r="D875" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E875" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F875" s="145" t="n">
+        <v>4106.67</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="33" t="n">
+        <v>703</v>
+      </c>
+      <c r="B876" s="34" t="inlineStr">
+        <is>
+          <t>5.9.40</t>
+        </is>
+      </c>
+      <c r="C876" s="35" t="inlineStr">
+        <is>
+          <t>Трубный хомут заземления МХ</t>
+        </is>
+      </c>
+      <c r="D876" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E876" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F876" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="33" t="n">
+        <v>704</v>
+      </c>
+      <c r="B877" s="34" t="inlineStr">
+        <is>
+          <t>5.11.9</t>
+        </is>
+      </c>
+      <c r="C877" s="35" t="inlineStr">
+        <is>
+          <t>Бетонная стяжка 50 мм</t>
+        </is>
+      </c>
+      <c r="D877" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E877" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F877" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="33" t="n">
+        <v>705</v>
+      </c>
+      <c r="B878" s="34" t="inlineStr">
+        <is>
+          <t>5.11.10</t>
+        </is>
+      </c>
+      <c r="C878" s="35" t="inlineStr">
+        <is>
+          <t>Бетонная стяжка 50-75 мм</t>
+        </is>
+      </c>
+      <c r="D878" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E878" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F878" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="33" t="n">
+        <v>706</v>
+      </c>
+      <c r="B879" s="34" t="inlineStr">
+        <is>
+          <t>5.11.11</t>
+        </is>
+      </c>
+      <c r="C879" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Установка нагревательных матов теплого пола в помещениях санузлов </t>
+        </is>
+      </c>
+      <c r="D879" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E879" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F879" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="33" t="n">
+        <v>707</v>
+      </c>
+      <c r="B880" s="34" t="inlineStr">
+        <is>
+          <t>5.11.12</t>
+        </is>
+      </c>
+      <c r="C880" s="35" t="inlineStr">
+        <is>
+          <t>Устройство обмазочной гидроизоляции полов во влажных помещениях</t>
+        </is>
+      </c>
+      <c r="D880" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E880" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F880" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="33" t="n">
+        <v>708</v>
+      </c>
+      <c r="B881" s="34" t="inlineStr">
+        <is>
+          <t>5.11.13</t>
+        </is>
+      </c>
+      <c r="C881" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Укладка напольной плитки керамической 600×600 мм в общих зонах </t>
+        </is>
+      </c>
+      <c r="D881" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E881" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F881" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="33" t="n">
+        <v>709</v>
+      </c>
+      <c r="B882" s="34" t="inlineStr">
+        <is>
+          <t>5.11.14</t>
+        </is>
+      </c>
+      <c r="C882" s="35" t="inlineStr">
+        <is>
+          <t>Укладка напольной плитки керамической с шероховатой поверхностью 600×600 мм мокрые зоны с/у и душевые</t>
+        </is>
+      </c>
+      <c r="D882" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E882" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F882" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="33" t="n">
+        <v>710</v>
+      </c>
+      <c r="B883" s="34" t="inlineStr">
+        <is>
+          <t>5.11.15</t>
+        </is>
+      </c>
+      <c r="C883" s="35" t="inlineStr">
+        <is>
+          <t>Укладка напольной плитки керамической с шероховатой поверхностью 300×300 мм лестницы</t>
+        </is>
+      </c>
+      <c r="D883" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E883" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F883" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="33" t="n">
+        <v>711</v>
+      </c>
+      <c r="B884" s="34" t="inlineStr">
+        <is>
+          <t>5.11.16</t>
+        </is>
+      </c>
+      <c r="C884" s="35" t="inlineStr">
+        <is>
+          <t>Укладка ламината промышленного 34 класса с подложкой и устроцством плинтуса МДФ</t>
+        </is>
+      </c>
+      <c r="D884" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E884" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F884" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="33" t="n">
+        <v>712</v>
+      </c>
+      <c r="B885" s="34" t="inlineStr">
+        <is>
+          <t>5.11.17</t>
+        </is>
+      </c>
+      <c r="C885" s="35" t="inlineStr">
+        <is>
+          <t>Устройство напольного покрытия из ковролина</t>
+        </is>
+      </c>
+      <c r="D885" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E885" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F885" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="33" t="n">
+        <v>713</v>
+      </c>
+      <c r="B886" s="34" t="inlineStr">
+        <is>
+          <t>5.11.18</t>
+        </is>
+      </c>
+      <c r="C886" s="35" t="inlineStr">
+        <is>
+          <t>Устройство покрытий из антистатического линолеума</t>
+        </is>
+      </c>
+      <c r="D886" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E886" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F886" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="33" t="n">
+        <v>714</v>
+      </c>
+      <c r="B887" s="34" t="inlineStr">
+        <is>
+          <t>5.11.19</t>
+        </is>
+      </c>
+      <c r="C887" s="35" t="inlineStr">
+        <is>
+          <t>Покраска пола полимерной краской</t>
+        </is>
+      </c>
+      <c r="D887" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E887" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F887" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="33" t="n">
+        <v>715</v>
+      </c>
+      <c r="B888" s="34" t="inlineStr">
+        <is>
+          <t>5.11.20</t>
+        </is>
+      </c>
+      <c r="C888" s="35" t="inlineStr">
+        <is>
+          <t>Гранит с термообработкой серого цвета на клеевой основе (входные группы)</t>
+        </is>
+      </c>
+      <c r="D888" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E888" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F888" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="33" t="n">
+        <v>716</v>
+      </c>
+      <c r="B889" s="34" t="inlineStr">
+        <is>
+          <t>5.12.4</t>
+        </is>
+      </c>
+      <c r="C889" s="35" t="inlineStr">
+        <is>
+          <t>Устройство стяжек из цементно-песчаного раствора М 150 50-85мм</t>
+        </is>
+      </c>
+      <c r="D889" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E889" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F889" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="33" t="n">
+        <v>717</v>
+      </c>
+      <c r="B890" s="34" t="inlineStr">
+        <is>
+          <t>5.12.5</t>
+        </is>
+      </c>
+      <c r="C890" s="35" t="inlineStr">
+        <is>
+          <t>Устройство стяжек из цементно-песчаного раствора М 150 50-75 мм</t>
+        </is>
+      </c>
+      <c r="D890" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E890" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F890" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="33" t="n">
+        <v>718</v>
+      </c>
+      <c r="B891" s="34" t="inlineStr">
+        <is>
+          <t>5.12.6</t>
+        </is>
+      </c>
+      <c r="C891" s="35" t="inlineStr">
+        <is>
+          <t>Самовыравнивающаяся смесь 30 мм (помещения и лестницы)</t>
+        </is>
+      </c>
+      <c r="D891" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E891" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F891" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="33" t="n">
+        <v>719</v>
+      </c>
+      <c r="B892" s="34" t="inlineStr">
+        <is>
+          <t>5.12.7</t>
+        </is>
+      </c>
+      <c r="C892" s="35" t="inlineStr">
+        <is>
+          <t>Самовыравнивающаяся смесь 10 мм</t>
+        </is>
+      </c>
+      <c r="D892" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E892" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F892" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="33" t="n">
+        <v>720</v>
+      </c>
+      <c r="B893" s="34" t="inlineStr">
+        <is>
+          <t>5.12.8</t>
+        </is>
+      </c>
+      <c r="C893" s="35" t="inlineStr">
+        <is>
+          <t>Самовыравнивающаяся смесь 17 мм</t>
+        </is>
+      </c>
+      <c r="D893" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E893" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F893" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="33" t="n">
+        <v>721</v>
+      </c>
+      <c r="B894" s="34" t="inlineStr">
+        <is>
+          <t>5.12.9</t>
+        </is>
+      </c>
+      <c r="C894" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Установка нагревательных матов теплого пола в помещениях санузлов </t>
+        </is>
+      </c>
+      <c r="D894" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E894" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F894" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="33" t="n">
+        <v>722</v>
+      </c>
+      <c r="B895" s="34" t="inlineStr">
+        <is>
+          <t>5.12.10</t>
+        </is>
+      </c>
+      <c r="C895" s="35" t="inlineStr">
+        <is>
+          <t>Устройство обмазочной гидроизоляции полов во влажных помещениях</t>
+        </is>
+      </c>
+      <c r="D895" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E895" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F895" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="33" t="n">
+        <v>723</v>
+      </c>
+      <c r="B896" s="34" t="inlineStr">
+        <is>
+          <t>5.12.11</t>
+        </is>
+      </c>
+      <c r="C896" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Укладка напольной плитки керамической поверхностью 600×600 мм в общих зонах </t>
+        </is>
+      </c>
+      <c r="D896" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E896" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F896" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="33" t="n">
+        <v>724</v>
+      </c>
+      <c r="B897" s="34" t="inlineStr">
+        <is>
+          <t>5.12.12</t>
+        </is>
+      </c>
+      <c r="C897" s="35" t="inlineStr">
+        <is>
+          <t>Укладка напольной плитки керамической с шероховатой поверхностью 600×600 мм в помещениях душевых и с/у</t>
+        </is>
+      </c>
+      <c r="D897" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E897" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F897" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="33" t="n">
+        <v>725</v>
+      </c>
+      <c r="B898" s="34" t="inlineStr">
+        <is>
+          <t>5.12.13</t>
+        </is>
+      </c>
+      <c r="C898" s="35" t="inlineStr">
+        <is>
+          <t>Укладка напольной плитки керамической с шероховатой поверхностью 300×300 мм лестницы</t>
+        </is>
+      </c>
+      <c r="D898" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E898" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F898" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="33" t="n">
+        <v>726</v>
+      </c>
+      <c r="B899" s="34" t="inlineStr">
+        <is>
+          <t>5.12.14</t>
+        </is>
+      </c>
+      <c r="C899" s="35" t="inlineStr">
+        <is>
+          <t>Укладка ламината промышленного 34 класса с подложкой и устроцством плинтуса МДФ</t>
+        </is>
+      </c>
+      <c r="D899" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E899" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F899" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="33" t="n">
+        <v>727</v>
+      </c>
+      <c r="B900" s="34" t="inlineStr">
+        <is>
+          <t>5.12.15</t>
+        </is>
+      </c>
+      <c r="C900" s="35" t="inlineStr">
+        <is>
+          <t>Покраска пола полимерной краской</t>
+        </is>
+      </c>
+      <c r="D900" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E900" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F900" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="33" t="n">
+        <v>728</v>
+      </c>
+      <c r="B901" s="34" t="inlineStr">
+        <is>
+          <t>5.12.16</t>
+        </is>
+      </c>
+      <c r="C901" s="35" t="inlineStr">
+        <is>
+          <t>Устройство покрытий из антистатического линолеума</t>
+        </is>
+      </c>
+      <c r="D901" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E901" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F901" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="33" t="n">
+        <v>729</v>
+      </c>
+      <c r="B902" s="34" t="inlineStr">
+        <is>
+          <t>5.12.17</t>
+        </is>
+      </c>
+      <c r="C902" s="35" t="inlineStr">
+        <is>
+          <t>Устройство спортивного резинового покрытия  в помещении спортзала</t>
+        </is>
+      </c>
+      <c r="D902" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E902" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F902" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="33" t="n">
+        <v>730</v>
+      </c>
+      <c r="B903" s="34" t="inlineStr">
+        <is>
+          <t>5.12.18</t>
+        </is>
+      </c>
+      <c r="C903" s="35" t="inlineStr">
+        <is>
+          <t>Звукоизоляция 5мм</t>
+        </is>
+      </c>
+      <c r="D903" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E903" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F903" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="33" t="n">
+        <v>731</v>
+      </c>
+      <c r="B904" s="34" t="inlineStr">
+        <is>
+          <t>5.12.19</t>
+        </is>
+      </c>
+      <c r="C904" s="35" t="inlineStr">
+        <is>
+          <t>Гранит с термообработкой серого цвета на клеевой основе (входные группы)</t>
+        </is>
+      </c>
+      <c r="D904" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E904" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F904" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="33" t="n">
+        <v>732</v>
+      </c>
+      <c r="B905" s="34" t="inlineStr">
+        <is>
+          <t>5.12.20</t>
+        </is>
+      </c>
+      <c r="C905" s="35" t="inlineStr">
+        <is>
+          <t>Плавающий пол в венткамере Гидроизоляция, пенополистирол 50мм, стяжка 50 мм М150</t>
+        </is>
+      </c>
+      <c r="D905" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E905" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F905" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="33" t="n">
+        <v>733</v>
+      </c>
+      <c r="B906" s="34" t="inlineStr">
+        <is>
+          <t>5.14.1</t>
+        </is>
+      </c>
+      <c r="C906" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛ тип 1 (облицовка с одной стороны)</t>
+        </is>
+      </c>
+      <c r="D906" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E906" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F906" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="33" t="n">
+        <v>734</v>
+      </c>
+      <c r="B907" s="34" t="inlineStr">
+        <is>
+          <t>5.14.2</t>
+        </is>
+      </c>
+      <c r="C907" s="35" t="inlineStr">
+        <is>
+          <t>Устройство обмазочной гидроизоляции стен и перегородок во влажных помещениях</t>
+        </is>
+      </c>
+      <c r="D907" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E907" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F907" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="33" t="n">
+        <v>735</v>
+      </c>
+      <c r="B908" s="34" t="inlineStr">
+        <is>
+          <t>5.14.3</t>
+        </is>
+      </c>
+      <c r="C908" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкцийГКЛ перегородок с шумоизоляцией тип 2 профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D908" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E908" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F908" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="33" t="n">
+        <v>736</v>
+      </c>
+      <c r="B909" s="34" t="inlineStr">
+        <is>
+          <t>5.14.4</t>
+        </is>
+      </c>
+      <c r="C909" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкцийГКЛ перегородок с шумоизоляцией тип 3 профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D909" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E909" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F909" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="33" t="n">
+        <v>737</v>
+      </c>
+      <c r="B910" s="34" t="inlineStr">
+        <is>
+          <t>5.14.5</t>
+        </is>
+      </c>
+      <c r="C910" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкцийГКЛ перегородок с шумоизоляцией тип 4 профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D910" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E910" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F910" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="33" t="n">
+        <v>738</v>
+      </c>
+      <c r="B911" s="34" t="inlineStr">
+        <is>
+          <t>5.14.6</t>
+        </is>
+      </c>
+      <c r="C911" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок во влажных зонах  тип 5 (облицовка с одной стороны)</t>
+        </is>
+      </c>
+      <c r="D911" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E911" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F911" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="33" t="n">
+        <v>739</v>
+      </c>
+      <c r="B912" s="34" t="inlineStr">
+        <is>
+          <t>5.14.7</t>
+        </is>
+      </c>
+      <c r="C912" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок с шумоизоляцией тип 6 профиль 50 мм</t>
+        </is>
+      </c>
+      <c r="D912" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E912" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F912" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="33" t="n">
+        <v>740</v>
+      </c>
+      <c r="B913" s="34" t="inlineStr">
+        <is>
+          <t>5.14.8</t>
+        </is>
+      </c>
+      <c r="C913" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок с шумоизоляцией тип 7 профиль 75 мм</t>
+        </is>
+      </c>
+      <c r="D913" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E913" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F913" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="33" t="n">
+        <v>741</v>
+      </c>
+      <c r="B914" s="34" t="inlineStr">
+        <is>
+          <t>5.14.9</t>
+        </is>
+      </c>
+      <c r="C914" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок с шумоизоляцией тип 8 профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D914" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E914" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F914" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="33" t="n">
+        <v>742</v>
+      </c>
+      <c r="B915" s="34" t="inlineStr">
+        <is>
+          <t>5.14.10</t>
+        </is>
+      </c>
+      <c r="C915" s="35" t="inlineStr">
+        <is>
+          <t>Подгоотовка  ГКЛ перегородок и ГКЛ стен к штукатурке:  проклейка швов, грунтовка</t>
+        </is>
+      </c>
+      <c r="D915" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E915" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F915" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="33" t="n">
+        <v>743</v>
+      </c>
+      <c r="B916" s="34" t="inlineStr">
+        <is>
+          <t>5.14.11</t>
+        </is>
+      </c>
+      <c r="C916" s="35" t="inlineStr">
+        <is>
+          <t>Перегородка поликарбонат 16 мм, профиль из анодированного алюминия. с раздвижным открыванием.
+(или аналог)</t>
+        </is>
+      </c>
+      <c r="D916" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E916" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F916" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="33" t="n">
+        <v>744</v>
+      </c>
+      <c r="B917" s="34" t="inlineStr">
+        <is>
+          <t>5.14.12</t>
+        </is>
+      </c>
+      <c r="C917" s="35" t="inlineStr">
+        <is>
+          <t>Штукатурка сухой смесью на гипсовой
+основе –1-1.5 мм;
+Выравнивающий финишный слой на гипсовой
+основе – 1 мм;</t>
+        </is>
+      </c>
+      <c r="D917" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E917" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F917" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="33" t="n">
+        <v>745</v>
+      </c>
+      <c r="B918" s="34" t="inlineStr">
+        <is>
+          <t>5.14.13</t>
+        </is>
+      </c>
+      <c r="C918" s="35" t="inlineStr">
+        <is>
+          <t>Штукатурка швов сухой смесью на
+цементной основе</t>
+        </is>
+      </c>
+      <c r="D918" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E918" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F918" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="33" t="n">
+        <v>746</v>
+      </c>
+      <c r="B919" s="34" t="inlineStr">
+        <is>
+          <t>5.14.14</t>
+        </is>
+      </c>
+      <c r="C919" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен акриловой краской в 2 слоя МОП ниже h=1,8м</t>
+        </is>
+      </c>
+      <c r="D919" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E919" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F919" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="33" t="n">
+        <v>747</v>
+      </c>
+      <c r="B920" s="34" t="inlineStr">
+        <is>
+          <t>5.14.15</t>
+        </is>
+      </c>
+      <c r="C920" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен водоэмульсионной  краской в 2 слоя МОП выше h=1,8м</t>
+        </is>
+      </c>
+      <c r="D920" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E920" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F920" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="33" t="n">
+        <v>748</v>
+      </c>
+      <c r="B921" s="34" t="inlineStr">
+        <is>
+          <t>5.14.16</t>
+        </is>
+      </c>
+      <c r="C921" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен водоэмульсионной краской в 2 слоя Жилые комнаты</t>
+        </is>
+      </c>
+      <c r="D921" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E921" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F921" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="33" t="n">
+        <v>749</v>
+      </c>
+      <c r="B922" s="34" t="inlineStr">
+        <is>
+          <t>5.14.17</t>
+        </is>
+      </c>
+      <c r="C922" s="35" t="inlineStr">
+        <is>
+          <t>Устройство настенных покрытий из керамической плитка в санузлах и душевых</t>
+        </is>
+      </c>
+      <c r="D922" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E922" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F922" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="33" t="n">
+        <v>750</v>
+      </c>
+      <c r="B923" s="34" t="inlineStr">
+        <is>
+          <t>5.14.18</t>
+        </is>
+      </c>
+      <c r="C923" s="35" t="inlineStr">
+        <is>
+          <t>Окраска видимых частей (не зашитых стеновыми и потолочными конструкциями) металлических конструкций эмалью ПФ 115 цвет RAL 7035</t>
+        </is>
+      </c>
+      <c r="D923" s="36" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="E923" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F923" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="33" t="n">
+        <v>751</v>
+      </c>
+      <c r="B924" s="34" t="inlineStr">
+        <is>
+          <t>5.14.19</t>
+        </is>
+      </c>
+      <c r="C924" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж подоконников 1280х350</t>
+        </is>
+      </c>
+      <c r="D924" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E924" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F924" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="33" t="n">
+        <v>752</v>
+      </c>
+      <c r="B925" s="34" t="inlineStr">
+        <is>
+          <t>5.15.1</t>
+        </is>
+      </c>
+      <c r="C925" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛ тип 1 (облицовка с одной стороны)</t>
+        </is>
+      </c>
+      <c r="D925" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E925" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F925" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="33" t="n">
+        <v>753</v>
+      </c>
+      <c r="B926" s="34" t="inlineStr">
+        <is>
+          <t>5.15.2</t>
+        </is>
+      </c>
+      <c r="C926" s="35" t="inlineStr">
+        <is>
+          <t>Устройство обмазочной гидроизоляции стен и перегородок во влажных помещениях</t>
+        </is>
+      </c>
+      <c r="D926" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E926" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F926" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="33" t="n">
+        <v>754</v>
+      </c>
+      <c r="B927" s="34" t="inlineStr">
+        <is>
+          <t>5.15.3</t>
+        </is>
+      </c>
+      <c r="C927" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкцийГКЛ перегородок с шумоизоляцией тип 2 профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D927" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E927" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F927" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="33" t="n">
+        <v>755</v>
+      </c>
+      <c r="B928" s="34" t="inlineStr">
+        <is>
+          <t>5.15.4</t>
+        </is>
+      </c>
+      <c r="C928" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкцийГКЛ перегородок с шумоизоляцией тип 3 (5) профиль 100 мм</t>
+        </is>
+      </c>
+      <c r="D928" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E928" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F928" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="33" t="n">
+        <v>756</v>
+      </c>
+      <c r="B929" s="34" t="inlineStr">
+        <is>
+          <t>5.15.5</t>
+        </is>
+      </c>
+      <c r="C929" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок во влажных зонах  тип 4 (облицовка с одной стороны)</t>
+        </is>
+      </c>
+      <c r="D929" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E929" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F929" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="33" t="n">
+        <v>757</v>
+      </c>
+      <c r="B930" s="34" t="inlineStr">
+        <is>
+          <t>5.15.6</t>
+        </is>
+      </c>
+      <c r="C930" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛВ перегородок с шумоизоляцией тип 5 (7)  профиль 50 мм</t>
+        </is>
+      </c>
+      <c r="D930" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E930" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F930" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="33" t="n">
+        <v>758</v>
+      </c>
+      <c r="B931" s="34" t="inlineStr">
+        <is>
+          <t>5.15.7</t>
+        </is>
+      </c>
+      <c r="C931" s="35" t="inlineStr">
+        <is>
+          <t>Подгоотовка  ГКЛ перегородок и ГКЛ стен к штукатурке:  проклейка швов, грунтовка</t>
+        </is>
+      </c>
+      <c r="D931" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E931" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F931" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="33" t="n">
+        <v>759</v>
+      </c>
+      <c r="B932" s="34" t="inlineStr">
+        <is>
+          <t>5.15.8</t>
+        </is>
+      </c>
+      <c r="C932" s="35" t="inlineStr">
+        <is>
+          <t>Перегородка поликарбонат 16 мм, профиль из анодированного алюминия. с раздвижным открыванием.
+(или аналог) 2200 мм</t>
+        </is>
+      </c>
+      <c r="D932" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E932" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F932" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="33" t="n">
+        <v>760</v>
+      </c>
+      <c r="B933" s="34" t="inlineStr">
+        <is>
+          <t>5.15.9</t>
+        </is>
+      </c>
+      <c r="C933" s="35" t="inlineStr">
+        <is>
+          <t>Штукатурка сухой смесью на гипсовой
+основе –1-1.5 мм;
+Выравнивающий финишный слой на гипсовой
+основе – 1 мм;</t>
+        </is>
+      </c>
+      <c r="D933" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E933" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F933" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="33" t="n">
+        <v>761</v>
+      </c>
+      <c r="B934" s="34" t="inlineStr">
+        <is>
+          <t>5.15.10</t>
+        </is>
+      </c>
+      <c r="C934" s="35" t="inlineStr">
+        <is>
+          <t>Штукатурка швов сухой смесью на цементной основе</t>
+        </is>
+      </c>
+      <c r="D934" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E934" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F934" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="33" t="n">
+        <v>762</v>
+      </c>
+      <c r="B935" s="34" t="inlineStr">
+        <is>
+          <t>5.15.11</t>
+        </is>
+      </c>
+      <c r="C935" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен акриловой краской в 2 слоя МОП ниже h=1,8м</t>
+        </is>
+      </c>
+      <c r="D935" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E935" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F935" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="33" t="n">
+        <v>763</v>
+      </c>
+      <c r="B936" s="34" t="inlineStr">
+        <is>
+          <t>5.15.12</t>
+        </is>
+      </c>
+      <c r="C936" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен водоэмульсионной  краской в 2 слоя МОП выше h=1,8м</t>
+        </is>
+      </c>
+      <c r="D936" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E936" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F936" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="33" t="n">
+        <v>764</v>
+      </c>
+      <c r="B937" s="34" t="inlineStr">
+        <is>
+          <t>5.15.13</t>
+        </is>
+      </c>
+      <c r="C937" s="35" t="inlineStr">
+        <is>
+          <t>Устройство настенных покрытий из керамической плитка в санузлах и душевых</t>
+        </is>
+      </c>
+      <c r="D937" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E937" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F937" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="33" t="n">
+        <v>765</v>
+      </c>
+      <c r="B938" s="34" t="inlineStr">
+        <is>
+          <t>5.15.14</t>
+        </is>
+      </c>
+      <c r="C938" s="35" t="inlineStr">
+        <is>
+          <t>Окраска видимых частей (не зашитых стеновыми и потолочными конструкциями) металлических конструкций эмалью ПФ 115 цвет RAL 7035</t>
+        </is>
+      </c>
+      <c r="D938" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E938" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F938" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="33" t="n">
+        <v>766</v>
+      </c>
+      <c r="B939" s="34" t="inlineStr">
+        <is>
+          <t>5.15.15</t>
+        </is>
+      </c>
+      <c r="C939" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж подоконников 1280х270</t>
+        </is>
+      </c>
+      <c r="D939" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E939" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F939" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="33" t="n">
+        <v>767</v>
+      </c>
+      <c r="B940" s="34" t="inlineStr">
+        <is>
+          <t>5.16.1</t>
+        </is>
+      </c>
+      <c r="C940" s="35" t="inlineStr">
+        <is>
+          <t>Устройство конструкций ГКЛ тип 1 (облицовка с одной стороны)</t>
+        </is>
+      </c>
+      <c r="D940" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E940" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F940" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="33" t="n">
+        <v>768</v>
+      </c>
+      <c r="B941" s="34" t="inlineStr">
+        <is>
+          <t>5.16.2</t>
+        </is>
+      </c>
+      <c r="C941" s="35" t="inlineStr">
+        <is>
+          <t>Подготовка  ГКЛ перегородок и ГКЛ стен к штукатурке:  проклейка швов, грунтовка</t>
+        </is>
+      </c>
+      <c r="D941" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E941" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F941" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="33" t="n">
+        <v>769</v>
+      </c>
+      <c r="B942" s="34" t="inlineStr">
+        <is>
+          <t>5.16.3</t>
+        </is>
+      </c>
+      <c r="C942" s="35" t="inlineStr">
+        <is>
+          <t>Штукатурка сухой смесью на гипсовой
+основе –1-1.5 мм;
+Выравнивающий финишный слой на гипсовой
+основе – 1 мм;</t>
+        </is>
+      </c>
+      <c r="D942" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E942" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F942" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="33" t="n">
+        <v>770</v>
+      </c>
+      <c r="B943" s="34" t="inlineStr">
+        <is>
+          <t>5.16.4</t>
+        </is>
+      </c>
+      <c r="C943" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен акриловой краской в 2 слоя МОП ниже h=1,8м</t>
+        </is>
+      </c>
+      <c r="D943" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E943" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F943" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="33" t="n">
+        <v>771</v>
+      </c>
+      <c r="B944" s="34" t="inlineStr">
+        <is>
+          <t>5.16.5</t>
+        </is>
+      </c>
+      <c r="C944" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ перегородок и ГКЛ стен водоэмульсионной  краской в 2 слоя МОП выше h=1,8м</t>
+        </is>
+      </c>
+      <c r="D944" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E944" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F944" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="33" t="n">
+        <v>772</v>
+      </c>
+      <c r="B945" s="34" t="inlineStr">
+        <is>
+          <t>5.16.6</t>
+        </is>
+      </c>
+      <c r="C945" s="35" t="inlineStr">
+        <is>
+          <t>Окраска видимых частей (не зашитых стеновыми и потолочными конструкциями) металлических конструкций эмалью ПФ 115 цвет RAL 7035</t>
+        </is>
+      </c>
+      <c r="D945" s="36" t="inlineStr">
+        <is>
+          <t>комплекс</t>
+        </is>
+      </c>
+      <c r="E945" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F945" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="33" t="n">
+        <v>773</v>
+      </c>
+      <c r="B946" s="34" t="inlineStr">
+        <is>
+          <t>5.16.7</t>
+        </is>
+      </c>
+      <c r="C946" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж подоконников 1280х270</t>
+        </is>
+      </c>
+      <c r="D946" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E946" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F946" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="33" t="n">
+        <v>774</v>
+      </c>
+      <c r="B947" s="34" t="inlineStr">
+        <is>
+          <t>5.17.1</t>
+        </is>
+      </c>
+      <c r="C947" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолков типа Армстронг 600×600 мм</t>
+        </is>
+      </c>
+      <c r="D947" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E947" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F947" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="33" t="n">
+        <v>775</v>
+      </c>
+      <c r="B948" s="34" t="inlineStr">
+        <is>
+          <t>5.17.2</t>
+        </is>
+      </c>
+      <c r="C948" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолков из металлических перфорированных панелей 600х600мм в помещениях санузлов</t>
+        </is>
+      </c>
+      <c r="D948" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E948" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F948" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="33" t="n">
+        <v>776</v>
+      </c>
+      <c r="B949" s="34" t="inlineStr">
+        <is>
+          <t>5.17.3</t>
+        </is>
+      </c>
+      <c r="C949" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолочных конструкций из  ГКЛ в 1 слой</t>
+        </is>
+      </c>
+      <c r="D949" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E949" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F949" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="33" t="n">
+        <v>777</v>
+      </c>
+      <c r="B950" s="34" t="inlineStr">
+        <is>
+          <t>5.17.4</t>
+        </is>
+      </c>
+      <c r="C950" s="35" t="inlineStr">
+        <is>
+          <t>Подгоотовка  ГКЛ потолков к окраске:  проклейка швов, грунтовка, финишная шпаклевка</t>
+        </is>
+      </c>
+      <c r="D950" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E950" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F950" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="33" t="n">
+        <v>778</v>
+      </c>
+      <c r="B951" s="34" t="inlineStr">
+        <is>
+          <t>5.17.5</t>
+        </is>
+      </c>
+      <c r="C951" s="35" t="inlineStr">
+        <is>
+          <t>Окраска  ГКЛ потолков водоэмульсионной краской  в 2 слоя</t>
+        </is>
+      </c>
+      <c r="D951" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E951" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F951" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="33" t="n">
+        <v>779</v>
+      </c>
+      <c r="B952" s="34" t="inlineStr">
+        <is>
+          <t>5.18.1</t>
+        </is>
+      </c>
+      <c r="C952" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолков типа Армстронг 600×600 мм</t>
+        </is>
+      </c>
+      <c r="D952" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E952" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F952" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="33" t="n">
+        <v>780</v>
+      </c>
+      <c r="B953" s="34" t="inlineStr">
+        <is>
+          <t>5.18.2</t>
+        </is>
+      </c>
+      <c r="C953" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолков из металлических перфорированных панелей 600х600мм в помещениях санузлов</t>
+        </is>
+      </c>
+      <c r="D953" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E953" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F953" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="33" t="n">
+        <v>781</v>
+      </c>
+      <c r="B954" s="34" t="inlineStr">
+        <is>
+          <t>5.19.1</t>
+        </is>
+      </c>
+      <c r="C954" s="35" t="inlineStr">
+        <is>
+          <t>Устройство потолков типа Армстронг 600×600 мм</t>
+        </is>
+      </c>
+      <c r="D954" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E954" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F954" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="33" t="n">
+        <v>782</v>
+      </c>
+      <c r="B955" s="34" t="inlineStr">
+        <is>
+          <t>5.20.1</t>
+        </is>
+      </c>
+      <c r="C955" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х700 (МДФ), в т.ч. наличники, замки и фурнитура 3*, 3 (Л,П)</t>
+        </is>
+      </c>
+      <c r="D955" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E955" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F955" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="33" t="n">
+        <v>783</v>
+      </c>
+      <c r="B956" s="34" t="inlineStr">
+        <is>
+          <t>5.20.2</t>
+        </is>
+      </c>
+      <c r="C956" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 (МДФ), в т.ч. наличники, замки и фурнитура  (Л, П) 2*, 2</t>
+        </is>
+      </c>
+      <c r="D956" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E956" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F956" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="33" t="n">
+        <v>784</v>
+      </c>
+      <c r="B957" s="34" t="inlineStr">
+        <is>
+          <t>5.20.3</t>
+        </is>
+      </c>
+      <c r="C957" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 (МДФ), в т.ч. наличники, замки и фурнитура 2Р, 2*Р</t>
+        </is>
+      </c>
+      <c r="D957" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E957" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F957" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="33" t="n">
+        <v>785</v>
+      </c>
+      <c r="B958" s="34" t="inlineStr">
+        <is>
+          <t>5.20.4</t>
+        </is>
+      </c>
+      <c r="C958" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Установка двери металической 2300х1450 П Внутренняя Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 4 </t>
+        </is>
+      </c>
+      <c r="D958" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E958" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F958" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="33" t="n">
+        <v>786</v>
+      </c>
+      <c r="B959" s="34" t="inlineStr">
+        <is>
+          <t>5.20.5</t>
+        </is>
+      </c>
+      <c r="C959" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери металической 2300х900 Л Внутренняя Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 6</t>
+        </is>
+      </c>
+      <c r="D959" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E959" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F959" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="33" t="n">
+        <v>787</v>
+      </c>
+      <c r="B960" s="34" t="inlineStr">
+        <is>
+          <t>5.20.6</t>
+        </is>
+      </c>
+      <c r="C960" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери металической 2300х900 П Внутренняя Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 7</t>
+        </is>
+      </c>
+      <c r="D960" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E960" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F960" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="33" t="n">
+        <v>788</v>
+      </c>
+      <c r="B961" s="34" t="inlineStr">
+        <is>
+          <t>5.20.7</t>
+        </is>
+      </c>
+      <c r="C961" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной металической 2300х1000 Л  Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 5</t>
+        </is>
+      </c>
+      <c r="D961" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E961" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F961" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="33" t="n">
+        <v>789</v>
+      </c>
+      <c r="B962" s="34" t="inlineStr">
+        <is>
+          <t>5.20.8</t>
+        </is>
+      </c>
+      <c r="C962" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной 2300х14500 Л (Алюминиевый профиль, теплая серия), в т.ч. наличники, замки и фурнитура 1*</t>
+        </is>
+      </c>
+      <c r="D962" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E962" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F962" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="33" t="n">
+        <v>790</v>
+      </c>
+      <c r="B963" s="34" t="inlineStr">
+        <is>
+          <t>5.20.9</t>
+        </is>
+      </c>
+      <c r="C963" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной  2300х14500 П (Алюминиевый профиль, теплая серия), в т.ч. наличники, замки и фурнитура 1</t>
+        </is>
+      </c>
+      <c r="D963" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E963" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F963" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="33" t="n">
+        <v>791</v>
+      </c>
+      <c r="B964" s="34" t="inlineStr">
+        <is>
+          <t>5.21.1</t>
+        </is>
+      </c>
+      <c r="C964" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 П (ПВХ), в т.ч. наличники, замки и фурнитура 1</t>
+        </is>
+      </c>
+      <c r="D964" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E964" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F964" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="33" t="n">
+        <v>792</v>
+      </c>
+      <c r="B965" s="34" t="inlineStr">
+        <is>
+          <t>5.21.2</t>
+        </is>
+      </c>
+      <c r="C965" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 Л (ПВХ), в т.ч. наличники, замки и фурнитура 1*</t>
+        </is>
+      </c>
+      <c r="D965" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E965" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F965" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="33" t="n">
+        <v>793</v>
+      </c>
+      <c r="B966" s="34" t="inlineStr">
+        <is>
+          <t>5.21.3</t>
+        </is>
+      </c>
+      <c r="C966" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х800 П (ПВХ), в т.ч. наличники, замки и фурнитура 2</t>
+        </is>
+      </c>
+      <c r="D966" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E966" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F966" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="33" t="n">
+        <v>794</v>
+      </c>
+      <c r="B967" s="34" t="inlineStr">
+        <is>
+          <t>5.21.4</t>
+        </is>
+      </c>
+      <c r="C967" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х800 Л (ПВХ), в т.ч. наличники, замки и фурнитура 2*</t>
+        </is>
+      </c>
+      <c r="D967" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E967" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F967" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="33" t="n">
+        <v>795</v>
+      </c>
+      <c r="B968" s="34" t="inlineStr">
+        <is>
+          <t>5.21.5</t>
+        </is>
+      </c>
+      <c r="C968" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х1450 П (ПВХ), в т.ч. наличники, замки и фурнитура 3</t>
+        </is>
+      </c>
+      <c r="D968" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E968" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F968" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="33" t="n">
+        <v>796</v>
+      </c>
+      <c r="B969" s="34" t="inlineStr">
+        <is>
+          <t>5.21.6</t>
+        </is>
+      </c>
+      <c r="C969" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х1450 Л (ПВХ), в т.ч. наличники, замки и фурнитура 3*</t>
+        </is>
+      </c>
+      <c r="D969" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E969" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F969" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="33" t="n">
+        <v>797</v>
+      </c>
+      <c r="B970" s="34" t="inlineStr">
+        <is>
+          <t>5.21.7</t>
+        </is>
+      </c>
+      <c r="C970" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери металической 2300х900 Л Внутренняя Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 7</t>
+        </is>
+      </c>
+      <c r="D970" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E970" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F970" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="33" t="n">
+        <v>798</v>
+      </c>
+      <c r="B971" s="34" t="inlineStr">
+        <is>
+          <t>5.21.8</t>
+        </is>
+      </c>
+      <c r="C971" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери металической 2300х1450 П Внутренняя Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 8</t>
+        </is>
+      </c>
+      <c r="D971" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E971" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F971" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="33" t="n">
+        <v>799</v>
+      </c>
+      <c r="B972" s="34" t="inlineStr">
+        <is>
+          <t>5.21.9</t>
+        </is>
+      </c>
+      <c r="C972" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 П (Алюминиевый профиль, матовое остекление), в т.ч. наличники, замки и фурнитура С/У 1/1</t>
+        </is>
+      </c>
+      <c r="D972" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E972" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F972" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="33" t="n">
+        <v>800</v>
+      </c>
+      <c r="B973" s="34" t="inlineStr">
+        <is>
+          <t>5.21.10</t>
+        </is>
+      </c>
+      <c r="C973" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х900 Л (Алюминиевый профиль, матовое остекление), в т.ч. наличники, замки и фурнитура С/У 1/1*</t>
+        </is>
+      </c>
+      <c r="D973" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E973" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F973" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="33" t="n">
+        <v>801</v>
+      </c>
+      <c r="B974" s="34" t="inlineStr">
+        <is>
+          <t>5.21.11</t>
+        </is>
+      </c>
+      <c r="C974" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х1450 П (Алюминиевый профиль), в т.ч. наличники, замки и фурнитура 3/1</t>
+        </is>
+      </c>
+      <c r="D974" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E974" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F974" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="33" t="n">
+        <v>802</v>
+      </c>
+      <c r="B975" s="34" t="inlineStr">
+        <is>
+          <t>5.21.12</t>
+        </is>
+      </c>
+      <c r="C975" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х1450 Л (Алюминиевый профиль), в т.ч. наличники, замки и фурнитура 3/1*</t>
+        </is>
+      </c>
+      <c r="D975" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E975" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F975" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="33" t="n">
+        <v>803</v>
+      </c>
+      <c r="B976" s="34" t="inlineStr">
+        <is>
+          <t>5.21.13</t>
+        </is>
+      </c>
+      <c r="C976" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х800 П (Алюминиевый профиль), в т.ч. наличники, замки и фурнитура 2/1</t>
+        </is>
+      </c>
+      <c r="D976" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E976" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F976" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="33" t="n">
+        <v>804</v>
+      </c>
+      <c r="B977" s="34" t="inlineStr">
+        <is>
+          <t>5.21.14</t>
+        </is>
+      </c>
+      <c r="C977" s="35" t="inlineStr">
+        <is>
+          <t>Установка межкомнатных дверей 2100х1450 П (Алюминиевый профиль), в т.ч. наличники, замки и фурнитура 10</t>
+        </is>
+      </c>
+      <c r="D977" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E977" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F977" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="33" t="n">
+        <v>805</v>
+      </c>
+      <c r="B978" s="34" t="inlineStr">
+        <is>
+          <t>5.21.15</t>
+        </is>
+      </c>
+      <c r="C978" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери 2200х800 (Поликарбонат 16мм) С/У и Душевые</t>
+        </is>
+      </c>
+      <c r="D978" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E978" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F978" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="33" t="n">
+        <v>806</v>
+      </c>
+      <c r="B979" s="34" t="inlineStr">
+        <is>
+          <t>5.21.16</t>
+        </is>
+      </c>
+      <c r="C979" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной  2300х14500 П (Алюминиевый профиль, теплая серия), в т.ч. наличники, замки и фурнитура</t>
+        </is>
+      </c>
+      <c r="D979" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E979" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F979" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="33" t="n">
+        <v>807</v>
+      </c>
+      <c r="B980" s="34" t="inlineStr">
+        <is>
+          <t>5.21.17</t>
+        </is>
+      </c>
+      <c r="C980" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной  2300х14500 Л (Алюминиевый профиль, теплая серия), в т.ч. наличники, замки и фурнитура</t>
+        </is>
+      </c>
+      <c r="D980" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E980" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F980" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="33" t="n">
+        <v>808</v>
+      </c>
+      <c r="B981" s="34" t="inlineStr">
+        <is>
+          <t>5.21.18</t>
+        </is>
+      </c>
+      <c r="C981" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной, металическая 2300х1450 П  Противопожарная ЕI30  в т.ч. наличники, замки и фурнитура 9</t>
+        </is>
+      </c>
+      <c r="D981" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E981" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F981" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="33" t="n">
+        <v>809</v>
+      </c>
+      <c r="B982" s="34" t="inlineStr">
+        <is>
+          <t>5.21.19</t>
+        </is>
+      </c>
+      <c r="C982" s="35" t="inlineStr">
+        <is>
+          <t>Установка внутренних витражей (В-3, В-4, В-5, В-6, В-7) (Алюминиевый профиль, теплая серия с термовставкой), в т.ч. наличники, замки и фурнитура 4</t>
+        </is>
+      </c>
+      <c r="D982" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E982" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F982" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="33" t="n">
+        <v>810</v>
+      </c>
+      <c r="B983" s="34" t="inlineStr">
+        <is>
+          <t>5.21.20</t>
+        </is>
+      </c>
+      <c r="C983" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной, металическая 2300х1450 П  Противопожарная ЕI45  в т.ч. наличники, замки и фурнитура 6</t>
+        </is>
+      </c>
+      <c r="D983" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E983" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F983" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="33" t="n">
+        <v>811</v>
+      </c>
+      <c r="B984" s="34" t="inlineStr">
+        <is>
+          <t>5.21.21</t>
+        </is>
+      </c>
+      <c r="C984" s="35" t="inlineStr">
+        <is>
+          <t>Установка двери наружной, металическая 2100х1000 Л  в т.ч. наличники, замки и фурнитура 5*</t>
+        </is>
+      </c>
+      <c r="D984" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E984" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F984" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="33" t="n">
+        <v>812</v>
+      </c>
+      <c r="B985" s="34" t="inlineStr">
+        <is>
+          <t>5.22.1</t>
+        </is>
+      </c>
+      <c r="C985" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж утеплителя 100мм 35кг/м3</t>
+        </is>
+      </c>
+      <c r="D985" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E985" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F985" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="33" t="n">
+        <v>813</v>
+      </c>
+      <c r="B986" s="34" t="inlineStr">
+        <is>
+          <t>5.22.2</t>
+        </is>
+      </c>
+      <c r="C986" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж мембраны профилированной</t>
+        </is>
+      </c>
+      <c r="D986" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E986" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F986" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="33" t="n">
+        <v>814</v>
+      </c>
+      <c r="B987" s="34" t="inlineStr">
+        <is>
+          <t>5.22.3</t>
+        </is>
+      </c>
+      <c r="C987" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сайдинга металлического 0,7мм на П-образном профиле</t>
+        </is>
+      </c>
+      <c r="D987" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E987" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F987" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="33" t="n">
+        <v>815</v>
+      </c>
+      <c r="B988" s="34" t="inlineStr">
+        <is>
+          <t>5.23.1</t>
+        </is>
+      </c>
+      <c r="C988" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж утеплителя 100мм 35кг/м3</t>
+        </is>
+      </c>
+      <c r="D988" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E988" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F988" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="33" t="n">
+        <v>816</v>
+      </c>
+      <c r="B989" s="34" t="inlineStr">
+        <is>
+          <t>5.23.2</t>
+        </is>
+      </c>
+      <c r="C989" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж мембраны профилированной</t>
+        </is>
+      </c>
+      <c r="D989" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E989" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F989" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="33" t="n">
+        <v>817</v>
+      </c>
+      <c r="B990" s="34" t="inlineStr">
+        <is>
+          <t>5.23.3</t>
+        </is>
+      </c>
+      <c r="C990" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сайдинга металлического 0,7мм на П-образном профиле</t>
+        </is>
+      </c>
+      <c r="D990" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E990" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F990" s="145" t="n">
+        <v>24104.51</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="33" t="n">
+        <v>818</v>
+      </c>
+      <c r="B991" s="34" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="C991" s="35" t="inlineStr">
+        <is>
+          <t>Разработка грунта для трубопроводов и колодцев, устройство основания, обратная засыпка с уплотнением</t>
+        </is>
+      </c>
+      <c r="D991" s="36" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E991" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F991" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="33" t="n">
+        <v>819</v>
+      </c>
+      <c r="B992" s="34" t="inlineStr">
+        <is>
+          <t>7.1.1.1</t>
+        </is>
+      </c>
+      <c r="C992" s="35" t="inlineStr">
+        <is>
+          <t>Разработка грунта</t>
+        </is>
+      </c>
+      <c r="D992" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E992" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F992" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="33" t="n">
+        <v>820</v>
+      </c>
+      <c r="B993" s="34" t="inlineStr">
+        <is>
+          <t>7.1.1.2</t>
+        </is>
+      </c>
+      <c r="C993" s="35" t="inlineStr">
+        <is>
+          <t>Устройство песчаного основания</t>
+        </is>
+      </c>
+      <c r="D993" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E993" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F993" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="33" t="n">
+        <v>821</v>
+      </c>
+      <c r="B994" s="34" t="inlineStr">
+        <is>
+          <t>7.1.1.3</t>
+        </is>
+      </c>
+      <c r="C994" s="35" t="inlineStr">
+        <is>
+          <t>Обратная засыпка с уплотнением</t>
+        </is>
+      </c>
+      <c r="D994" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E994" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F994" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="33" t="n">
+        <v>822</v>
+      </c>
+      <c r="B995" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2</t>
+        </is>
+      </c>
+      <c r="C995" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж колодцев в комплекте и прокладка труб В1,В2</t>
+        </is>
+      </c>
+      <c r="D995" s="36" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E995" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F995" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="33" t="n">
+        <v>823</v>
+      </c>
+      <c r="B996" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.1</t>
+        </is>
+      </c>
+      <c r="C996" s="35" t="inlineStr">
+        <is>
+          <t>Колодцы В1,В2</t>
+        </is>
+      </c>
+      <c r="D996" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E996" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F996" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="33" t="n">
+        <v>824</v>
+      </c>
+      <c r="B997" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.2</t>
+        </is>
+      </c>
+      <c r="C997" s="35" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная Ø57х3 мм</t>
+        </is>
+      </c>
+      <c r="D997" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E997" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F997" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="33" t="n">
+        <v>825</v>
+      </c>
+      <c r="B998" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.3</t>
+        </is>
+      </c>
+      <c r="C998" s="35" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная Ø89х4 мм</t>
+        </is>
+      </c>
+      <c r="D998" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E998" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F998" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="33" t="n">
+        <v>826</v>
+      </c>
+      <c r="B999" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.4</t>
+        </is>
+      </c>
+      <c r="C999" s="35" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная Ø108х4 мм</t>
+        </is>
+      </c>
+      <c r="D999" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E999" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F999" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="33" t="n">
+        <v>827</v>
+      </c>
+      <c r="B1000" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.5</t>
+        </is>
+      </c>
+      <c r="C1000" s="35" t="inlineStr">
+        <is>
+          <t>Футляр стальной  Ø273х4 мм</t>
+        </is>
+      </c>
+      <c r="D1000" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1000" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1000" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="33" t="n">
+        <v>828</v>
+      </c>
+      <c r="B1001" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.6</t>
+        </is>
+      </c>
+      <c r="C1001" s="35" t="inlineStr">
+        <is>
+          <t>Задвижка фланцевая  Ø100мм</t>
+        </is>
+      </c>
+      <c r="D1001" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1001" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1001" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="33" t="n">
+        <v>829</v>
+      </c>
+      <c r="B1002" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.7</t>
+        </is>
+      </c>
+      <c r="C1002" s="35" t="inlineStr">
+        <is>
+          <t>Задвижка фланцевая  Ø80мм</t>
+        </is>
+      </c>
+      <c r="D1002" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1002" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1002" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="33" t="n">
+        <v>830</v>
+      </c>
+      <c r="B1003" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.8</t>
+        </is>
+      </c>
+      <c r="C1003" s="35" t="inlineStr">
+        <is>
+          <t>Задвижка фланцевая  Ø50мм</t>
+        </is>
+      </c>
+      <c r="D1003" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1003" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1003" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="33" t="n">
+        <v>831</v>
+      </c>
+      <c r="B1004" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.9</t>
+        </is>
+      </c>
+      <c r="C1004" s="35" t="inlineStr">
+        <is>
+          <t>Люк водопроводный тяжелые</t>
+        </is>
+      </c>
+      <c r="D1004" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1004" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1004" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="33" t="n">
+        <v>832</v>
+      </c>
+      <c r="B1005" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.10</t>
+        </is>
+      </c>
+      <c r="C1005" s="35" t="inlineStr">
+        <is>
+          <t>Противопожарный гидрант</t>
+        </is>
+      </c>
+      <c r="D1005" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1005" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1005" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="33" t="n">
+        <v>833</v>
+      </c>
+      <c r="B1006" s="34" t="inlineStr">
+        <is>
+          <t>7.1.2.11</t>
+        </is>
+      </c>
+      <c r="C1006" s="35" t="inlineStr">
+        <is>
+          <t>Кран сливной ф25</t>
+        </is>
+      </c>
+      <c r="D1006" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1006" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1006" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="33" t="n">
+        <v>834</v>
+      </c>
+      <c r="B1007" s="34" t="inlineStr">
+        <is>
+          <t>7.2.1</t>
+        </is>
+      </c>
+      <c r="C1007" s="35" t="inlineStr">
+        <is>
+          <t>Разработка грунта для трубопроводов и колодцев, устройство основания, обратная засыпка с уплотнением</t>
+        </is>
+      </c>
+      <c r="D1007" s="36" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E1007" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1007" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="33" t="n">
+        <v>835</v>
+      </c>
+      <c r="B1008" s="34" t="inlineStr">
+        <is>
+          <t>7.2.1.2</t>
+        </is>
+      </c>
+      <c r="C1008" s="35" t="inlineStr">
+        <is>
+          <t>Устройство песчаного основания</t>
+        </is>
+      </c>
+      <c r="D1008" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1008" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1008" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="33" t="n">
+        <v>836</v>
+      </c>
+      <c r="B1009" s="34" t="inlineStr">
+        <is>
+          <t>7.2.1.3</t>
+        </is>
+      </c>
+      <c r="C1009" s="35" t="inlineStr">
+        <is>
+          <t>Обратная засыпка с уплотнением</t>
+        </is>
+      </c>
+      <c r="D1009" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1009" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1009" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="33" t="n">
+        <v>837</v>
+      </c>
+      <c r="B1010" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2</t>
+        </is>
+      </c>
+      <c r="C1010" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж колодцев в комплекте и прокладка труб К1</t>
+        </is>
+      </c>
+      <c r="D1010" s="36" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E1010" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1010" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="33" t="n">
+        <v>838</v>
+      </c>
+      <c r="B1011" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2.1</t>
+        </is>
+      </c>
+      <c r="C1011" s="35" t="inlineStr">
+        <is>
+          <t>Колодцы К1</t>
+        </is>
+      </c>
+      <c r="D1011" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1011" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1011" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="33" t="n">
+        <v>839</v>
+      </c>
+      <c r="B1012" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2.2</t>
+        </is>
+      </c>
+      <c r="C1012" s="35" t="inlineStr">
+        <is>
+          <t>Трубы канализационные ПВХ  Ø110мм</t>
+        </is>
+      </c>
+      <c r="D1012" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1012" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1012" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="33" t="n">
+        <v>840</v>
+      </c>
+      <c r="B1013" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2.3</t>
+        </is>
+      </c>
+      <c r="C1013" s="35" t="inlineStr">
+        <is>
+          <t>Трубы канализационные асбестоцементная  Ø150мм</t>
+        </is>
+      </c>
+      <c r="D1013" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1013" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1013" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="33" t="n">
+        <v>841</v>
+      </c>
+      <c r="B1014" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2.4</t>
+        </is>
+      </c>
+      <c r="C1014" s="35" t="inlineStr">
+        <is>
+          <t>Трубы канализационные асбестоцементная  Ø200мм</t>
+        </is>
+      </c>
+      <c r="D1014" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1014" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1014" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="33" t="n">
+        <v>842</v>
+      </c>
+      <c r="B1015" s="34" t="inlineStr">
+        <is>
+          <t>7.2.2.5</t>
+        </is>
+      </c>
+      <c r="C1015" s="35" t="inlineStr">
+        <is>
+          <t>Люки канализационные тяжелые</t>
+        </is>
+      </c>
+      <c r="D1015" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1015" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1015" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="33" t="n">
+        <v>843</v>
+      </c>
+      <c r="B1016" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1</t>
+        </is>
+      </c>
+      <c r="C1016" s="35" t="inlineStr">
+        <is>
+          <t>Разработка грунта, устройство бетонной подготовки, монтаж лотков, камер</t>
+        </is>
+      </c>
+      <c r="D1016" s="36" t="n"/>
+      <c r="E1016" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1016" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="33" t="n">
+        <v>844</v>
+      </c>
+      <c r="B1017" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.1</t>
+        </is>
+      </c>
+      <c r="C1017" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разработка грунта </t>
+        </is>
+      </c>
+      <c r="D1017" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1017" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1017" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="33" t="n">
+        <v>845</v>
+      </c>
+      <c r="B1018" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.2</t>
+        </is>
+      </c>
+      <c r="C1018" s="35" t="inlineStr">
+        <is>
+          <t>Обратная засыпка</t>
+        </is>
+      </c>
+      <c r="D1018" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1018" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1018" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="33" t="n">
+        <v>846</v>
+      </c>
+      <c r="B1019" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.3</t>
+        </is>
+      </c>
+      <c r="C1019" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бетонной подготовки В 7.5 (лоток)</t>
+        </is>
+      </c>
+      <c r="D1019" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1019" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1019" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="33" t="n">
+        <v>847</v>
+      </c>
+      <c r="B1020" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.4</t>
+        </is>
+      </c>
+      <c r="C1020" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сборных ЖБ Серия 3.006.1-2.87 (лоток)</t>
+        </is>
+      </c>
+      <c r="D1020" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1020" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1020" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="33" t="n">
+        <v>848</v>
+      </c>
+      <c r="B1021" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.5</t>
+        </is>
+      </c>
+      <c r="C1021" s="35" t="inlineStr">
+        <is>
+          <t>Жб конструкции бетон В25 с к/а 26,26 кг/м3 (лоток)</t>
+        </is>
+      </c>
+      <c r="D1021" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1021" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1021" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="33" t="n">
+        <v>849</v>
+      </c>
+      <c r="B1022" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.6</t>
+        </is>
+      </c>
+      <c r="C1022" s="35" t="inlineStr">
+        <is>
+          <t>Опорные конструкции КМ</t>
+        </is>
+      </c>
+      <c r="D1022" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E1022" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1022" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="33" t="n">
+        <v>850</v>
+      </c>
+      <c r="B1023" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.7</t>
+        </is>
+      </c>
+      <c r="C1023" s="35" t="inlineStr">
+        <is>
+          <t>Опоры неподвижные лобовые: Т3.02 - Т3.08</t>
+        </is>
+      </c>
+      <c r="D1023" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1023" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1023" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="33" t="n">
+        <v>851</v>
+      </c>
+      <c r="B1024" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.8</t>
+        </is>
+      </c>
+      <c r="C1024" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бетонной подготовки В 7,5 (камера)</t>
+        </is>
+      </c>
+      <c r="D1024" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1024" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1024" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="33" t="n">
+        <v>852</v>
+      </c>
+      <c r="B1025" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.9</t>
+        </is>
+      </c>
+      <c r="C1025" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сборных Ж/б (камера)</t>
+        </is>
+      </c>
+      <c r="D1025" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1025" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1025" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="33" t="n">
+        <v>853</v>
+      </c>
+      <c r="B1026" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.10</t>
+        </is>
+      </c>
+      <c r="C1026" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж КМ (люки, стремянки) (камера) 2х2</t>
+        </is>
+      </c>
+      <c r="D1026" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E1026" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1026" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="33" t="n">
+        <v>854</v>
+      </c>
+      <c r="B1027" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.11</t>
+        </is>
+      </c>
+      <c r="C1027" s="35" t="inlineStr">
+        <is>
+          <t>Жб конструкции бетон В15 с к/а 21,5 кг/м3 (камера)</t>
+        </is>
+      </c>
+      <c r="D1027" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1027" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1027" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="33" t="n">
+        <v>855</v>
+      </c>
+      <c r="B1028" s="34" t="inlineStr">
+        <is>
+          <t>7.3.1.12</t>
+        </is>
+      </c>
+      <c r="C1028" s="35" t="inlineStr">
+        <is>
+          <t>Молнтаж закладных изделий и сальников 14шт (камера)</t>
+        </is>
+      </c>
+      <c r="D1028" s="36" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E1028" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1028" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="33" t="n">
+        <v>856</v>
+      </c>
+      <c r="B1029" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2</t>
+        </is>
+      </c>
+      <c r="C1029" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов и арматуры тепловой сети</t>
+        </is>
+      </c>
+      <c r="D1029" s="36" t="n"/>
+      <c r="E1029" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1029" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="33" t="n">
+        <v>857</v>
+      </c>
+      <c r="B1030" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.1</t>
+        </is>
+      </c>
+      <c r="C1030" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 133х4</t>
+        </is>
+      </c>
+      <c r="D1030" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1030" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1030" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="33" t="n">
+        <v>858</v>
+      </c>
+      <c r="B1031" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.2</t>
+        </is>
+      </c>
+      <c r="C1031" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 108х4</t>
+        </is>
+      </c>
+      <c r="D1031" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1031" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1031" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="33" t="n">
+        <v>859</v>
+      </c>
+      <c r="B1032" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.3</t>
+        </is>
+      </c>
+      <c r="C1032" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 89х3,5</t>
+        </is>
+      </c>
+      <c r="D1032" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1032" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1032" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="33" t="n">
+        <v>860</v>
+      </c>
+      <c r="B1033" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.4</t>
+        </is>
+      </c>
+      <c r="C1033" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 76х3</t>
+        </is>
+      </c>
+      <c r="D1033" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1033" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1033" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="33" t="n">
+        <v>861</v>
+      </c>
+      <c r="B1034" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.5</t>
+        </is>
+      </c>
+      <c r="C1034" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 57х3</t>
+        </is>
+      </c>
+      <c r="D1034" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1034" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1034" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="33" t="n">
+        <v>862</v>
+      </c>
+      <c r="B1035" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.6</t>
+        </is>
+      </c>
+      <c r="C1035" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 40х3</t>
+        </is>
+      </c>
+      <c r="D1035" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1035" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1035" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="33" t="n">
+        <v>863</v>
+      </c>
+      <c r="B1036" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.7</t>
+        </is>
+      </c>
+      <c r="C1036" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб ф 25х2,8</t>
+        </is>
+      </c>
+      <c r="D1036" s="36" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E1036" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1036" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="33" t="n">
+        <v>864</v>
+      </c>
+      <c r="B1037" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.8</t>
+        </is>
+      </c>
+      <c r="C1037" s="35" t="inlineStr">
+        <is>
+          <t>Изоляция труб органо-силикатная АС-8а (ОС-51-03)/ четыре слоя с отвердителем /ТУ84-725-83</t>
+        </is>
+      </c>
+      <c r="D1037" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1037" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1037" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="33" t="n">
+        <v>865</v>
+      </c>
+      <c r="B1038" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.9</t>
+        </is>
+      </c>
+      <c r="C1038" s="35" t="inlineStr">
+        <is>
+          <t>Теплоизоляционное покрытие труб минераловатными матами  прошивными М100</t>
+        </is>
+      </c>
+      <c r="D1038" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1038" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1038" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="33" t="n">
+        <v>866</v>
+      </c>
+      <c r="B1039" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.10</t>
+        </is>
+      </c>
+      <c r="C1039" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж стеклопластика РСТ ТУ 6-11-145-80</t>
+        </is>
+      </c>
+      <c r="D1039" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1039" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1039" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="33" t="n">
+        <v>867</v>
+      </c>
+      <c r="B1040" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.11</t>
+        </is>
+      </c>
+      <c r="C1040" s="35" t="inlineStr">
+        <is>
+          <t>Обертывание изолированных труб металической сеткой и штукатурка</t>
+        </is>
+      </c>
+      <c r="D1040" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1040" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1040" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="33" t="n">
+        <v>868</v>
+      </c>
+      <c r="B1041" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.12</t>
+        </is>
+      </c>
+      <c r="C1041" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опора неподвижная лобовая </t>
+        </is>
+      </c>
+      <c r="D1041" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1041" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1041" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="33" t="n">
+        <v>869</v>
+      </c>
+      <c r="B1042" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.13</t>
+        </is>
+      </c>
+      <c r="C1042" s="35" t="inlineStr">
+        <is>
+          <t>Опора скользящая</t>
+        </is>
+      </c>
+      <c r="D1042" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1042" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1042" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="33" t="n">
+        <v>870</v>
+      </c>
+      <c r="B1043" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.14</t>
+        </is>
+      </c>
+      <c r="C1043" s="35" t="inlineStr">
+        <is>
+          <t>Фасонные элементы</t>
+        </is>
+      </c>
+      <c r="D1043" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1043" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1043" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="33" t="n">
+        <v>871</v>
+      </c>
+      <c r="B1044" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.15</t>
+        </is>
+      </c>
+      <c r="C1044" s="35" t="inlineStr">
+        <is>
+          <t>Арматура (краны шаровые ф25-125 Р=2,5 Мпа</t>
+        </is>
+      </c>
+      <c r="D1044" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1044" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1044" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="33" t="n">
+        <v>872</v>
+      </c>
+      <c r="B1045" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.16</t>
+        </is>
+      </c>
+      <c r="C1045" s="35" t="inlineStr">
+        <is>
+          <t>Узел герметизации ввода трубопроводов тепловой сети</t>
+        </is>
+      </c>
+      <c r="D1045" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1045" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1045" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="33" t="n">
+        <v>873</v>
+      </c>
+      <c r="B1046" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.17</t>
+        </is>
+      </c>
+      <c r="C1046" s="35" t="inlineStr">
+        <is>
+          <t>Люк чугунный "Т" ф 700</t>
+        </is>
+      </c>
+      <c r="D1046" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1046" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1046" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="33" t="n">
+        <v>874</v>
+      </c>
+      <c r="B1047" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.18</t>
+        </is>
+      </c>
+      <c r="C1047" s="35" t="inlineStr">
+        <is>
+          <t>Узел управления №1 (отопление и вентиляция) АБК</t>
+        </is>
+      </c>
+      <c r="D1047" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1047" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1047" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="33" t="n">
+        <v>875</v>
+      </c>
+      <c r="B1048" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.19</t>
+        </is>
+      </c>
+      <c r="C1048" s="35" t="inlineStr">
+        <is>
+          <t>Узел управления №2 (ГВС) АБК</t>
+        </is>
+      </c>
+      <c r="D1048" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1048" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1048" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="33" t="n">
+        <v>876</v>
+      </c>
+      <c r="B1049" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.20</t>
+        </is>
+      </c>
+      <c r="C1049" s="35" t="inlineStr">
+        <is>
+          <t>Узел управления №3 (отопление) Общежитие</t>
+        </is>
+      </c>
+      <c r="D1049" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1049" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1049" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="33" t="n">
+        <v>877</v>
+      </c>
+      <c r="B1050" s="34" t="inlineStr">
+        <is>
+          <t>7.3.2.21</t>
+        </is>
+      </c>
+      <c r="C1050" s="35" t="inlineStr">
+        <is>
+          <t>Узел управления №4 (ГВС) Общежитие</t>
+        </is>
+      </c>
+      <c r="D1050" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1050" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1050" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="33" t="n">
+        <v>878</v>
+      </c>
+      <c r="B1051" s="34" t="inlineStr">
+        <is>
+          <t>7.4.1</t>
+        </is>
+      </c>
+      <c r="C1051" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разработка грунта </t>
+        </is>
+      </c>
+      <c r="D1051" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1051" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1051" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="33" t="n">
+        <v>879</v>
+      </c>
+      <c r="B1052" s="34" t="inlineStr">
+        <is>
+          <t>7.4.2</t>
+        </is>
+      </c>
+      <c r="C1052" s="35" t="inlineStr">
+        <is>
+          <t>Обратная засыпка просеянной землей или песком</t>
+        </is>
+      </c>
+      <c r="D1052" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1052" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1052" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="33" t="n">
+        <v>880</v>
+      </c>
+      <c r="B1053" s="34" t="inlineStr">
+        <is>
+          <t>7.4.3</t>
+        </is>
+      </c>
+      <c r="C1053" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сигнальной ленты rexant 150 mm 19-3015</t>
+        </is>
+      </c>
+      <c r="D1053" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1053" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1053" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="33" t="n">
+        <v>881</v>
+      </c>
+      <c r="B1054" s="34" t="inlineStr">
+        <is>
+          <t>7.4.4</t>
+        </is>
+      </c>
+      <c r="C1054" s="35" t="inlineStr">
+        <is>
+          <t>Обратная засыпка</t>
+        </is>
+      </c>
+      <c r="D1054" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1054" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1054" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="33" t="n">
+        <v>882</v>
+      </c>
+      <c r="B1055" s="34" t="inlineStr">
+        <is>
+          <t>7.4.5</t>
+        </is>
+      </c>
+      <c r="C1055" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж труб асбестоцементных Д-200</t>
+        </is>
+      </c>
+      <c r="D1055" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1055" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1055" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="33" t="n">
+        <v>883</v>
+      </c>
+      <c r="B1056" s="34" t="inlineStr">
+        <is>
+          <t>7.4.6</t>
+        </is>
+      </c>
+      <c r="C1056" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж кожуха А11-2011.51, 4 анкера</t>
+        </is>
+      </c>
+      <c r="D1056" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1056" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1056" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="33" t="n">
+        <v>884</v>
+      </c>
+      <c r="B1057" s="34" t="inlineStr">
+        <is>
+          <t>7.4.7</t>
+        </is>
+      </c>
+      <c r="C1057" s="35" t="inlineStr">
+        <is>
+          <t>Прокладка силового кабеля в траншее КЛ-0,4кВ АВВБ 3х150+1х70 мм</t>
+        </is>
+      </c>
+      <c r="D1057" s="36" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="E1057" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1057" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="33" t="n">
+        <v>885</v>
+      </c>
+      <c r="B1058" s="34" t="inlineStr">
+        <is>
+          <t>7.4.8</t>
+        </is>
+      </c>
+      <c r="C1058" s="35" t="inlineStr">
+        <is>
+          <t>Прокладка силового кабеля в траншее КЛ-0,4кВ АВВБ 3х185+1х95 мм</t>
+        </is>
+      </c>
+      <c r="D1058" s="36" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="E1058" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1058" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="33" t="n">
+        <v>886</v>
+      </c>
+      <c r="B1059" s="34" t="inlineStr">
+        <is>
+          <t>7.4.9</t>
+        </is>
+      </c>
+      <c r="C1059" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж выключателя автоматического ВА88-40 400 А</t>
+        </is>
+      </c>
+      <c r="D1059" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1059" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1059" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="33" t="n">
+        <v>887</v>
+      </c>
+      <c r="B1060" s="34" t="inlineStr">
+        <is>
+          <t>7.4.10</t>
+        </is>
+      </c>
+      <c r="C1060" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж выключателя автоматического ВА88-40 315 А</t>
+        </is>
+      </c>
+      <c r="D1060" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1060" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1060" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="33" t="n">
+        <v>888</v>
+      </c>
+      <c r="B1061" s="34" t="inlineStr">
+        <is>
+          <t>7.4.11</t>
+        </is>
+      </c>
+      <c r="C1061" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж муфт кабельных концевых 4КВНТп-1-150/240</t>
+        </is>
+      </c>
+      <c r="D1061" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1061" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1061" s="145" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="33" t="n">
+        <v>889</v>
+      </c>
+      <c r="B1062" s="34" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C1062" s="35" t="inlineStr">
+        <is>
+          <t>Подготовительные работы</t>
+        </is>
+      </c>
+      <c r="D1062" s="36" t="n"/>
+      <c r="E1062" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1062" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="33" t="n">
+        <v>890</v>
+      </c>
+      <c r="B1063" s="34" t="inlineStr">
+        <is>
+          <t>8.1.1</t>
+        </is>
+      </c>
+      <c r="C1063" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Демонтаж существующего забора </t>
+        </is>
+      </c>
+      <c r="D1063" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1063" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1063" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="33" t="n">
+        <v>891</v>
+      </c>
+      <c r="B1064" s="34" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C1064" s="35" t="inlineStr">
+        <is>
+          <t>Покрытие Тип 1 (Щебеночное покрытие проездов и площадок)</t>
+        </is>
+      </c>
+      <c r="D1064" s="36" t="n"/>
+      <c r="E1064" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1064" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="33" t="n">
+        <v>892</v>
+      </c>
+      <c r="B1065" s="34" t="inlineStr">
+        <is>
+          <t>8.2.1</t>
+        </is>
+      </c>
+      <c r="C1065" s="35" t="inlineStr">
+        <is>
+          <t>Уплотнение грунта основания</t>
+        </is>
+      </c>
+      <c r="D1065" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1065" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1065" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="33" t="n">
+        <v>893</v>
+      </c>
+      <c r="B1066" s="34" t="inlineStr">
+        <is>
+          <t>8.2.2</t>
+        </is>
+      </c>
+      <c r="C1066" s="35" t="inlineStr">
+        <is>
+          <t>Песчано-щебеночная смесь 150мм 40/60</t>
+        </is>
+      </c>
+      <c r="D1066" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1066" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1066" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="33" t="n">
+        <v>894</v>
+      </c>
+      <c r="B1067" s="34" t="inlineStr">
+        <is>
+          <t>8.2.3</t>
+        </is>
+      </c>
+      <c r="C1067" s="35" t="inlineStr">
+        <is>
+          <t>Покрытие щебень фракционированный 20-40 мм с заклинкой-мелким щебнем, марка по прочности не менее 350 МПа, марка по дробимости М800, И-3, F50 по ГОСТ 32703-2014 h- 250мм</t>
+        </is>
+      </c>
+      <c r="D1067" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1067" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1067" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="33" t="n">
+        <v>895</v>
+      </c>
+      <c r="B1068" s="34" t="inlineStr">
+        <is>
+          <t>8.2.4</t>
+        </is>
+      </c>
+      <c r="C1068" s="35" t="inlineStr">
+        <is>
+          <t>Обочина щебень фракционированный, уложенный 150мм</t>
+        </is>
+      </c>
+      <c r="D1068" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1068" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1068" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="33" t="n">
+        <v>896</v>
+      </c>
+      <c r="B1069" s="34" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C1069" s="35" t="inlineStr">
+        <is>
+          <t>Покрытие Tип 11 из брусчатки с возможностью проезда  (в Рабочем проекте)</t>
+        </is>
+      </c>
+      <c r="D1069" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1069" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1069" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="33" t="n">
+        <v>897</v>
+      </c>
+      <c r="B1070" s="34" t="inlineStr">
+        <is>
+          <t>8.3.1</t>
+        </is>
+      </c>
+      <c r="C1070" s="35" t="inlineStr">
+        <is>
+          <t>Уплотнение грунта основания</t>
+        </is>
+      </c>
+      <c r="D1070" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1070" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1070" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="33" t="n">
+        <v>898</v>
+      </c>
+      <c r="B1071" s="34" t="inlineStr">
+        <is>
+          <t>8.3.2</t>
+        </is>
+      </c>
+      <c r="C1071" s="35" t="inlineStr">
+        <is>
+          <t>Песчаная подушка 150мм</t>
+        </is>
+      </c>
+      <c r="D1071" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1071" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1071" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="33" t="n">
+        <v>899</v>
+      </c>
+      <c r="B1072" s="34" t="inlineStr">
+        <is>
+          <t>8.3.3</t>
+        </is>
+      </c>
+      <c r="C1072" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж геотекстиль иглопробивной 200г/м2</t>
+        </is>
+      </c>
+      <c r="D1072" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1072" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1072" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="33" t="n">
+        <v>900</v>
+      </c>
+      <c r="B1073" s="34" t="inlineStr">
+        <is>
+          <t>8.3.4</t>
+        </is>
+      </c>
+      <c r="C1073" s="35" t="inlineStr">
+        <is>
+          <t>Бордюр из бортового камня БР 100.15.10 на бетонном основании</t>
+        </is>
+      </c>
+      <c r="D1073" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1073" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1073" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="33" t="n">
+        <v>901</v>
+      </c>
+      <c r="B1074" s="34" t="inlineStr">
+        <is>
+          <t>8.3.5</t>
+        </is>
+      </c>
+      <c r="C1074" s="35" t="inlineStr">
+        <is>
+          <t>Щебеночная подушка 20-40мм 200мм</t>
+        </is>
+      </c>
+      <c r="D1074" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1074" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1074" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="33" t="n">
+        <v>902</v>
+      </c>
+      <c r="B1075" s="34" t="inlineStr">
+        <is>
+          <t>8.3.6</t>
+        </is>
+      </c>
+      <c r="C1075" s="35" t="inlineStr">
+        <is>
+          <t>Песчаное основание укрепленное 10% цемента 40мм</t>
+        </is>
+      </c>
+      <c r="D1075" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1075" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1075" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="33" t="n">
+        <v>903</v>
+      </c>
+      <c r="B1076" s="34" t="inlineStr">
+        <is>
+          <t>8.3.7</t>
+        </is>
+      </c>
+      <c r="C1076" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж бетонная плитка Б.1.К8 по ГОСТ 17608-2017 - 0,08</t>
+        </is>
+      </c>
+      <c r="D1076" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1076" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1076" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="33" t="n">
+        <v>904</v>
+      </c>
+      <c r="B1077" s="34" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="C1077" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Покрытие Tип III из брусчатки  </t>
+        </is>
+      </c>
+      <c r="D1077" s="36" t="n"/>
+      <c r="E1077" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1077" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="33" t="n">
+        <v>905</v>
+      </c>
+      <c r="B1078" s="34" t="inlineStr">
+        <is>
+          <t>8.4.1</t>
+        </is>
+      </c>
+      <c r="C1078" s="35" t="inlineStr">
+        <is>
+          <t>Уплотнение грунта основания</t>
+        </is>
+      </c>
+      <c r="D1078" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1078" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1078" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="33" t="n">
+        <v>906</v>
+      </c>
+      <c r="B1079" s="34" t="inlineStr">
+        <is>
+          <t>8.4.2</t>
+        </is>
+      </c>
+      <c r="C1079" s="35" t="inlineStr">
+        <is>
+          <t>Устройство щебеночного основания 220мм</t>
+        </is>
+      </c>
+      <c r="D1079" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1079" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1079" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="33" t="n">
+        <v>907</v>
+      </c>
+      <c r="B1080" s="34" t="inlineStr">
+        <is>
+          <t>8.4.3</t>
+        </is>
+      </c>
+      <c r="C1080" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бордюра из бортового камня БР 100.20.8 на бетонном основании</t>
+        </is>
+      </c>
+      <c r="D1080" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1080" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1080" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="33" t="n">
+        <v>908</v>
+      </c>
+      <c r="B1081" s="34" t="inlineStr">
+        <is>
+          <t>8.4.4</t>
+        </is>
+      </c>
+      <c r="C1081" s="35" t="inlineStr">
+        <is>
+          <t>Устройство песчаного основания укрепленного 10% цемента 40мм</t>
+        </is>
+      </c>
+      <c r="D1081" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1081" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1081" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="33" t="n">
+        <v>909</v>
+      </c>
+      <c r="B1082" s="34" t="inlineStr">
+        <is>
+          <t>8.4.5</t>
+        </is>
+      </c>
+      <c r="C1082" s="35" t="inlineStr">
+        <is>
+          <t>Укладка бетонной плитки Б.7.К6 по ГОСТ 17608-2017 - 0,06м.</t>
+        </is>
+      </c>
+      <c r="D1082" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1082" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1082" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="33" t="n">
+        <v>910</v>
+      </c>
+      <c r="B1083" s="34" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="C1083" s="35" t="inlineStr">
+        <is>
+          <t>Отмостка Тип IV</t>
+        </is>
+      </c>
+      <c r="D1083" s="36" t="n"/>
+      <c r="E1083" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1083" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="33" t="n">
+        <v>911</v>
+      </c>
+      <c r="B1084" s="34" t="inlineStr">
+        <is>
+          <t>8.5.1</t>
+        </is>
+      </c>
+      <c r="C1084" s="35" t="inlineStr">
+        <is>
+          <t>Уплотнение основания</t>
+        </is>
+      </c>
+      <c r="D1084" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1084" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1084" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="33" t="n">
+        <v>912</v>
+      </c>
+      <c r="B1085" s="34" t="inlineStr">
+        <is>
+          <t>8.5.2</t>
+        </is>
+      </c>
+      <c r="C1085" s="35" t="inlineStr">
+        <is>
+          <t>Устройство слоя из песчано-щебеночной смеси 150мм 40/60</t>
+        </is>
+      </c>
+      <c r="D1085" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1085" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1085" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="33" t="n">
+        <v>913</v>
+      </c>
+      <c r="B1086" s="34" t="inlineStr">
+        <is>
+          <t>8.5.3</t>
+        </is>
+      </c>
+      <c r="C1086" s="35" t="inlineStr">
+        <is>
+          <t>Гидроизоляция (ПВХ пленка)</t>
+        </is>
+      </c>
+      <c r="D1086" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1086" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1086" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="33" t="n">
+        <v>914</v>
+      </c>
+      <c r="B1087" s="34" t="inlineStr">
+        <is>
+          <t>8.5.4</t>
+        </is>
+      </c>
+      <c r="C1087" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж геотекстиля иглопробивного 200г/м2</t>
+        </is>
+      </c>
+      <c r="D1087" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1087" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1087" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="33" t="n">
+        <v>915</v>
+      </c>
+      <c r="B1088" s="34" t="inlineStr">
+        <is>
+          <t>8.5.5</t>
+        </is>
+      </c>
+      <c r="C1088" s="35" t="inlineStr">
+        <is>
+          <t>Устройство основания из гравийной смеси 100мм</t>
+        </is>
+      </c>
+      <c r="D1088" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1088" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1088" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="33" t="n">
+        <v>916</v>
+      </c>
+      <c r="B1089" s="34" t="inlineStr">
+        <is>
+          <t>8.5.6</t>
+        </is>
+      </c>
+      <c r="C1089" s="35" t="inlineStr">
+        <is>
+          <t>Устройство отмостки из бетона кл В15, армированного сеткой ф10 А111 200*200 80мм</t>
+        </is>
+      </c>
+      <c r="D1089" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1089" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1089" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="33" t="n">
+        <v>917</v>
+      </c>
+      <c r="B1090" s="34" t="inlineStr">
+        <is>
+          <t>8.5.7</t>
+        </is>
+      </c>
+      <c r="C1090" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бордюра из бортового камня БР 100.20.8 на бетонном основании</t>
+        </is>
+      </c>
+      <c r="D1090" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1090" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1090" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="33" t="n">
+        <v>918</v>
+      </c>
+      <c r="B1091" s="34" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="C1091" s="35" t="inlineStr">
+        <is>
+          <t>Укрепление откосов</t>
+        </is>
+      </c>
+      <c r="D1091" s="36" t="n"/>
+      <c r="E1091" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1091" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="33" t="n">
+        <v>919</v>
+      </c>
+      <c r="B1092" s="34" t="inlineStr">
+        <is>
+          <t>8.6.1</t>
+        </is>
+      </c>
+      <c r="C1092" s="35" t="inlineStr">
+        <is>
+          <t>Укрепление откосов камнем булыжным, ГОСТ 22132-76</t>
+        </is>
+      </c>
+      <c r="D1092" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1092" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1092" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="33" t="n">
+        <v>920</v>
+      </c>
+      <c r="B1093" s="34" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="C1093" s="35" t="inlineStr">
+        <is>
+          <t>Водоотводные сооружения, озеленение, забор</t>
+        </is>
+      </c>
+      <c r="D1093" s="36" t="n"/>
+      <c r="E1093" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1093" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="33" t="n">
+        <v>921</v>
+      </c>
+      <c r="B1094" s="34" t="inlineStr">
+        <is>
+          <t>8.7.1</t>
+        </is>
+      </c>
+      <c r="C1094" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж лотка водоотводного бетонного 30.43.31 с решеткой</t>
+        </is>
+      </c>
+      <c r="D1094" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1094" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1094" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="33" t="n">
+        <v>922</v>
+      </c>
+      <c r="B1095" s="34" t="inlineStr">
+        <is>
+          <t>8.7.2</t>
+        </is>
+      </c>
+      <c r="C1095" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бетонной обоймы В15</t>
+        </is>
+      </c>
+      <c r="D1095" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1095" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1095" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="33" t="n">
+        <v>923</v>
+      </c>
+      <c r="B1096" s="34" t="inlineStr">
+        <is>
+          <t>8.7.3</t>
+        </is>
+      </c>
+      <c r="C1096" s="35" t="inlineStr">
+        <is>
+          <t>Устройство цементно-песчаной стяжки М100</t>
+        </is>
+      </c>
+      <c r="D1096" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1096" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1096" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="33" t="n">
+        <v>924</v>
+      </c>
+      <c r="B1097" s="34" t="inlineStr">
+        <is>
+          <t>8.7.4</t>
+        </is>
+      </c>
+      <c r="C1097" s="35" t="inlineStr">
+        <is>
+          <t>Устройство подушки песчано-гравийной 100мм</t>
+        </is>
+      </c>
+      <c r="D1097" s="36" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E1097" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1097" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="33" t="n">
+        <v>925</v>
+      </c>
+      <c r="B1098" s="34" t="inlineStr">
+        <is>
+          <t>8.7.5</t>
+        </is>
+      </c>
+      <c r="C1098" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж арычного блока БА-3 БА-3 ГОСТ 24547-81</t>
+        </is>
+      </c>
+      <c r="D1098" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1098" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1098" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="33" t="n">
+        <v>926</v>
+      </c>
+      <c r="B1099" s="34" t="inlineStr">
+        <is>
+          <t>8.7.6</t>
+        </is>
+      </c>
+      <c r="C1099" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж водопропускной трубы d-500мм,ГОСТ 24547-2016</t>
+        </is>
+      </c>
+      <c r="D1099" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1099" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1099" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="33" t="n">
+        <v>927</v>
+      </c>
+      <c r="B1100" s="34" t="inlineStr">
+        <is>
+          <t>8.7.7</t>
+        </is>
+      </c>
+      <c r="C1100" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж сборных телескопических лотков Б-6 (серия 3.503.1-66)</t>
+        </is>
+      </c>
+      <c r="D1100" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1100" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1100" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="33" t="n">
+        <v>928</v>
+      </c>
+      <c r="B1101" s="34" t="inlineStr">
+        <is>
+          <t>8.7.8</t>
+        </is>
+      </c>
+      <c r="C1101" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж смотрового блока,перекрытого металлической решеткой</t>
+        </is>
+      </c>
+      <c r="D1101" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1101" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1101" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="33" t="n">
+        <v>929</v>
+      </c>
+      <c r="B1102" s="34" t="inlineStr">
+        <is>
+          <t>8.7.9</t>
+        </is>
+      </c>
+      <c r="C1102" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж дождеприёмника чугунного ДБ ( ГОСТ 3634-2019)</t>
+        </is>
+      </c>
+      <c r="D1102" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1102" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1102" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="33" t="n">
+        <v>930</v>
+      </c>
+      <c r="B1103" s="34" t="inlineStr">
+        <is>
+          <t>8.7.10</t>
+        </is>
+      </c>
+      <c r="C1103" s="35" t="inlineStr">
+        <is>
+          <t>Устройство бордюра из бортового камня БР 100.30.15 на бетонном основании</t>
+        </is>
+      </c>
+      <c r="D1103" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1103" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1103" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="33" t="n">
+        <v>931</v>
+      </c>
+      <c r="B1104" s="34" t="inlineStr">
+        <is>
+          <t>8.7.11</t>
+        </is>
+      </c>
+      <c r="C1104" s="35" t="inlineStr">
+        <is>
+          <t>Посадка ели 7-12 лет</t>
+        </is>
+      </c>
+      <c r="D1104" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1104" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1104" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="33" t="n">
+        <v>932</v>
+      </c>
+      <c r="B1105" s="34" t="inlineStr">
+        <is>
+          <t>8.7.12</t>
+        </is>
+      </c>
+      <c r="C1105" s="35" t="inlineStr">
+        <is>
+          <t>Посадка можжевельника 7-12 лет</t>
+        </is>
+      </c>
+      <c r="D1105" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1105" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1105" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="33" t="n">
+        <v>933</v>
+      </c>
+      <c r="B1106" s="34" t="inlineStr">
+        <is>
+          <t>8.7.13</t>
+        </is>
+      </c>
+      <c r="C1106" s="35" t="inlineStr">
+        <is>
+          <t>Посадка туи западной 3-4 лет</t>
+        </is>
+      </c>
+      <c r="D1106" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1106" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1106" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="33" t="n">
+        <v>934</v>
+      </c>
+      <c r="B1107" s="34" t="inlineStr">
+        <is>
+          <t>8.7.14</t>
+        </is>
+      </c>
+      <c r="C1107" s="35" t="inlineStr">
+        <is>
+          <t>Посадка жимолости 5-7 лет</t>
+        </is>
+      </c>
+      <c r="D1107" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1107" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1107" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="33" t="n">
+        <v>935</v>
+      </c>
+      <c r="B1108" s="34" t="inlineStr">
+        <is>
+          <t>8.7.15</t>
+        </is>
+      </c>
+      <c r="C1108" s="35" t="inlineStr">
+        <is>
+          <t>Посадка туи западной снежноягодника</t>
+        </is>
+      </c>
+      <c r="D1108" s="36" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E1108" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1108" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="33" t="n">
+        <v>936</v>
+      </c>
+      <c r="B1109" s="34" t="inlineStr">
+        <is>
+          <t>8.7.16</t>
+        </is>
+      </c>
+      <c r="C1109" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внесение растительного слоя 200мм  с семянами газонная трава (травосмесь мятлик луговой, овсяница красная, полевица обыкновенная) </t>
+        </is>
+      </c>
+      <c r="D1109" s="36" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E1109" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1109" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="33" t="n">
+        <v>937</v>
+      </c>
+      <c r="B1110" s="34" t="inlineStr">
+        <is>
+          <t>8.7.17</t>
+        </is>
+      </c>
+      <c r="C1110" s="35" t="inlineStr">
+        <is>
+          <t>Установка скамейки "Вдохновение"</t>
+        </is>
+      </c>
+      <c r="D1110" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1110" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1110" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="33" t="n">
+        <v>938</v>
+      </c>
+      <c r="B1111" s="34" t="inlineStr">
+        <is>
+          <t>8.7.18</t>
+        </is>
+      </c>
+      <c r="C1111" s="35" t="inlineStr">
+        <is>
+          <t>Установка урны со вставкой и подставкой для основания</t>
+        </is>
+      </c>
+      <c r="D1111" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1111" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1111" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="33" t="n">
+        <v>939</v>
+      </c>
+      <c r="B1112" s="34" t="inlineStr">
+        <is>
+          <t>8.7.19</t>
+        </is>
+      </c>
+      <c r="C1112" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж навеса над мусорными баками на 2 шт.</t>
+        </is>
+      </c>
+      <c r="D1112" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1112" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1112" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="33" t="n">
+        <v>940</v>
+      </c>
+      <c r="B1113" s="34" t="inlineStr">
+        <is>
+          <t>8.7.20</t>
+        </is>
+      </c>
+      <c r="C1113" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж контейнера для ТБО"Евро"</t>
+        </is>
+      </c>
+      <c r="D1113" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1113" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1113" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="33" t="n">
+        <v>941</v>
+      </c>
+      <c r="B1114" s="34" t="inlineStr">
+        <is>
+          <t>8.7.21</t>
+        </is>
+      </c>
+      <c r="C1114" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж противопожарного щита в комплекте</t>
+        </is>
+      </c>
+      <c r="D1114" s="36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1114" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1114" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="33" t="n">
+        <v>942</v>
+      </c>
+      <c r="B1115" s="34" t="inlineStr">
+        <is>
+          <t>8.7.22</t>
+        </is>
+      </c>
+      <c r="C1115" s="35" t="inlineStr">
+        <is>
+          <t>Монтаж забора (13,28 т, 39,02м3 фунд)</t>
+        </is>
+      </c>
+      <c r="D1115" s="36" t="inlineStr">
+        <is>
+          <t>м/п</t>
+        </is>
+      </c>
+      <c r="E1115" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1115" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="33" t="n">
+        <v>943</v>
+      </c>
+      <c r="B1116" s="34" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="C1116" s="35" t="inlineStr">
+        <is>
+          <t>Демобилизация</t>
+        </is>
+      </c>
+      <c r="D1116" s="36" t="n"/>
+      <c r="E1116" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1116" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="33" t="n">
+        <v>944</v>
+      </c>
+      <c r="B1117" s="34" t="inlineStr">
+        <is>
+          <t>8.8.1</t>
+        </is>
+      </c>
+      <c r="C1117" s="35" t="inlineStr">
+        <is>
+          <t>Демобилизация</t>
+        </is>
+      </c>
+      <c r="D1117" s="36" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E1117" s="144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1117" s="145" t="n">
+        <v>29907.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0"/>
